--- a/data/tournaments_master.xlsx
+++ b/data/tournaments_master.xlsx
@@ -513,10 +513,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>76809</t>
-        </is>
+      <c r="A2" t="n">
+        <v>76809</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -592,15 +590,13 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>77283</t>
-        </is>
+      <c r="A3" t="n">
+        <v>77283</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -676,15 +672,13 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>300226</t>
-        </is>
+      <c r="A4" t="n">
+        <v>300226</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -760,15 +754,13 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>300239</t>
-        </is>
+      <c r="A5" t="n">
+        <v>300239</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -844,15 +836,13 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>76811</t>
-        </is>
+      <c r="A6" t="n">
+        <v>76811</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -928,15 +918,13 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>76945</t>
-        </is>
+      <c r="A7" t="n">
+        <v>76945</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1012,15 +1000,13 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>76817</t>
-        </is>
+      <c r="A8" t="n">
+        <v>76817</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1096,15 +1082,13 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>77310</t>
-        </is>
+      <c r="A9" t="n">
+        <v>77310</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1180,15 +1164,13 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>300207</t>
-        </is>
+      <c r="A10" t="n">
+        <v>300207</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1264,15 +1246,13 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>76820</t>
-        </is>
+      <c r="A11" t="n">
+        <v>76820</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1348,15 +1328,13 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>76948</t>
-        </is>
+      <c r="A12" t="n">
+        <v>76948</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1432,15 +1410,13 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>77181</t>
-        </is>
+      <c r="A13" t="n">
+        <v>77181</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1516,15 +1492,13 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>77186</t>
-        </is>
+      <c r="A14" t="n">
+        <v>77186</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1600,15 +1574,13 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>76974</t>
-        </is>
+      <c r="A15" t="n">
+        <v>76974</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1684,15 +1656,13 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>77065</t>
-        </is>
+      <c r="A16" t="n">
+        <v>77065</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1768,15 +1738,13 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>300299</t>
-        </is>
+      <c r="A17" t="n">
+        <v>300299</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1852,15 +1820,13 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>300304</t>
-        </is>
+      <c r="A18" t="n">
+        <v>300304</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1936,15 +1902,13 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>300321</t>
-        </is>
+      <c r="A19" t="n">
+        <v>300321</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2020,15 +1984,13 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>300370</t>
-        </is>
+      <c r="A20" t="n">
+        <v>300370</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2104,15 +2066,13 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>76951</t>
-        </is>
+      <c r="A21" t="n">
+        <v>76951</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2188,15 +2148,13 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>77081</t>
-        </is>
+      <c r="A22" t="n">
+        <v>77081</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2272,15 +2230,13 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>77145</t>
-        </is>
+      <c r="A23" t="n">
+        <v>77145</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2356,15 +2312,13 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>77342</t>
-        </is>
+      <c r="A24" t="n">
+        <v>77342</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2440,15 +2394,13 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>76977</t>
-        </is>
+      <c r="A25" t="n">
+        <v>76977</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2524,15 +2476,13 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>300103</t>
-        </is>
+      <c r="A26" t="n">
+        <v>300103</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2608,15 +2558,13 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>300249</t>
-        </is>
+      <c r="A27" t="n">
+        <v>300249</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2692,15 +2640,13 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>300331</t>
-        </is>
+      <c r="A28" t="n">
+        <v>300331</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2776,15 +2722,13 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>300457</t>
-        </is>
+      <c r="A29" t="n">
+        <v>300457</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2860,15 +2804,13 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>76954</t>
-        </is>
+      <c r="A30" t="n">
+        <v>76954</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2944,15 +2886,13 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>76980</t>
-        </is>
+      <c r="A31" t="n">
+        <v>76980</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3028,15 +2968,13 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>300289</t>
-        </is>
+      <c r="A32" t="n">
+        <v>300289</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -3112,15 +3050,13 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>300427</t>
-        </is>
+      <c r="A33" t="n">
+        <v>300427</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3196,15 +3132,13 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>300452</t>
-        </is>
+      <c r="A34" t="n">
+        <v>300452</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3280,15 +3214,13 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>300556</t>
-        </is>
+      <c r="A35" t="n">
+        <v>300556</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3364,15 +3296,13 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>300590</t>
-        </is>
+      <c r="A36" t="n">
+        <v>300590</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3448,15 +3378,13 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>300571</t>
-        </is>
+      <c r="A37" t="n">
+        <v>300571</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3532,15 +3460,13 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>300162</t>
-        </is>
+      <c r="A38" t="n">
+        <v>300162</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3616,15 +3542,13 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>300326</t>
-        </is>
+      <c r="A39" t="n">
+        <v>300326</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3700,15 +3624,13 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>300547</t>
-        </is>
+      <c r="A40" t="n">
+        <v>300547</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3784,15 +3706,13 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>300565</t>
-        </is>
+      <c r="A41" t="n">
+        <v>300565</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3868,15 +3788,13 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>300618</t>
-        </is>
+      <c r="A42" t="n">
+        <v>300618</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3952,15 +3870,13 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>300676</t>
-        </is>
+      <c r="A43" t="n">
+        <v>300676</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -4036,15 +3952,13 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>300116</t>
-        </is>
+      <c r="A44" t="n">
+        <v>300116</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4120,15 +4034,13 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>300263</t>
-        </is>
+      <c r="A45" t="n">
+        <v>300263</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -4204,15 +4116,13 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>300458</t>
-        </is>
+      <c r="A46" t="n">
+        <v>300458</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4288,15 +4198,13 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>300658</t>
-        </is>
+      <c r="A47" t="n">
+        <v>300658</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -4372,15 +4280,13 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>300705</t>
-        </is>
+      <c r="A48" t="n">
+        <v>300705</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -4456,15 +4362,13 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>300912</t>
-        </is>
+      <c r="A49" t="n">
+        <v>300912</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -4540,15 +4444,13 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>77289</t>
-        </is>
+      <c r="A50" t="n">
+        <v>77289</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -4624,15 +4526,13 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>77291</t>
-        </is>
+      <c r="A51" t="n">
+        <v>77291</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -4708,15 +4608,13 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>300562</t>
-        </is>
+      <c r="A52" t="n">
+        <v>300562</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4792,15 +4690,13 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>300893</t>
-        </is>
+      <c r="A53" t="n">
+        <v>300893</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -4876,15 +4772,13 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>300574</t>
-        </is>
+      <c r="A54" t="n">
+        <v>300574</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -4960,15 +4854,13 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>300813</t>
-        </is>
+      <c r="A55" t="n">
+        <v>300813</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -5044,15 +4936,13 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>300817</t>
-        </is>
+      <c r="A56" t="n">
+        <v>300817</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -5128,15 +5018,13 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>300738</t>
-        </is>
+      <c r="A57" t="n">
+        <v>300738</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -5212,15 +5100,13 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>300767</t>
-        </is>
+      <c r="A58" t="n">
+        <v>300767</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -5296,15 +5182,13 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>300944</t>
-        </is>
+      <c r="A59" t="n">
+        <v>300944</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -5380,15 +5264,13 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>300753</t>
-        </is>
+      <c r="A60" t="n">
+        <v>300753</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -5464,15 +5346,13 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>300204</t>
-        </is>
+      <c r="A61" t="n">
+        <v>300204</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -5548,15 +5428,13 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>300470</t>
-        </is>
+      <c r="A62" t="n">
+        <v>300470</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -5632,15 +5510,13 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>300872</t>
-        </is>
+      <c r="A63" t="n">
+        <v>300872</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -5716,15 +5592,13 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>301056</t>
-        </is>
+      <c r="A64" t="n">
+        <v>301056</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -5800,15 +5674,13 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>301090</t>
-        </is>
+      <c r="A65" t="n">
+        <v>301090</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -5884,15 +5756,13 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>301179</t>
-        </is>
+      <c r="A66" t="n">
+        <v>301179</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -5968,15 +5838,13 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>77297</t>
-        </is>
+      <c r="A67" t="n">
+        <v>77297</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -6052,15 +5920,13 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>77299</t>
-        </is>
+      <c r="A68" t="n">
+        <v>77299</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -6136,15 +6002,13 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>300201</t>
-        </is>
+      <c r="A69" t="n">
+        <v>300201</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -6220,15 +6084,13 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>300648</t>
-        </is>
+      <c r="A70" t="n">
+        <v>300648</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -6304,15 +6166,13 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>300744</t>
-        </is>
+      <c r="A71" t="n">
+        <v>300744</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -6388,15 +6248,13 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>301077</t>
-        </is>
+      <c r="A72" t="n">
+        <v>301077</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -6472,15 +6330,13 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>301095</t>
-        </is>
+      <c r="A73" t="n">
+        <v>301095</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -6556,15 +6412,13 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>301352</t>
-        </is>
+      <c r="A74" t="n">
+        <v>301352</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -6640,15 +6494,13 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>301355</t>
-        </is>
+      <c r="A75" t="n">
+        <v>301355</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -6724,15 +6576,13 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>300193</t>
-        </is>
+      <c r="A76" t="n">
+        <v>300193</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -6808,15 +6658,13 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>300196</t>
-        </is>
+      <c r="A77" t="n">
+        <v>300196</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -6892,15 +6740,13 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>300189</t>
-        </is>
+      <c r="A78" t="n">
+        <v>300189</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -6976,15 +6822,13 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>300669</t>
-        </is>
+      <c r="A79" t="n">
+        <v>300669</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -7060,15 +6904,13 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>300672</t>
-        </is>
+      <c r="A80" t="n">
+        <v>300672</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -7144,15 +6986,13 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>300747</t>
-        </is>
+      <c r="A81" t="n">
+        <v>300747</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -7228,15 +7068,13 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>300993</t>
-        </is>
+      <c r="A82" t="n">
+        <v>300993</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -7312,15 +7150,13 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>301049</t>
-        </is>
+      <c r="A83" t="n">
+        <v>301049</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -7396,15 +7232,13 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>301062</t>
-        </is>
+      <c r="A84" t="n">
+        <v>301062</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -7480,15 +7314,13 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>301063</t>
-        </is>
+      <c r="A85" t="n">
+        <v>301063</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -7564,15 +7396,13 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>300762</t>
-        </is>
+      <c r="A86" t="n">
+        <v>300762</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -7648,15 +7478,13 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>301134</t>
-        </is>
+      <c r="A87" t="n">
+        <v>301134</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -7732,15 +7560,13 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>301172</t>
-        </is>
+      <c r="A88" t="n">
+        <v>301172</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -7816,15 +7642,13 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>301285</t>
-        </is>
+      <c r="A89" t="n">
+        <v>301285</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -7900,15 +7724,13 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>301298</t>
-        </is>
+      <c r="A90" t="n">
+        <v>301298</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -7984,15 +7806,13 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>301358</t>
-        </is>
+      <c r="A91" t="n">
+        <v>301358</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -8068,15 +7888,13 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>301361</t>
-        </is>
+      <c r="A92" t="n">
+        <v>301361</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -8152,15 +7970,13 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>301370</t>
-        </is>
+      <c r="A93" t="n">
+        <v>301370</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -8236,15 +8052,13 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>301395</t>
-        </is>
+      <c r="A94" t="n">
+        <v>301395</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -8320,15 +8134,13 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>301400</t>
-        </is>
+      <c r="A95" t="n">
+        <v>301400</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -8404,15 +8216,13 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>301402</t>
-        </is>
+      <c r="A96" t="n">
+        <v>301402</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -8488,15 +8298,13 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>300217</t>
-        </is>
+      <c r="A97" t="n">
+        <v>300217</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -8572,15 +8380,13 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>300220</t>
-        </is>
+      <c r="A98" t="n">
+        <v>300220</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -8656,15 +8462,13 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>301137</t>
-        </is>
+      <c r="A99" t="n">
+        <v>301137</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -8740,15 +8544,13 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>300284</t>
-        </is>
+      <c r="A100" t="n">
+        <v>300284</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -8824,15 +8626,13 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>301260</t>
-        </is>
+      <c r="A101" t="n">
+        <v>301260</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -8908,15 +8708,13 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>301420</t>
-        </is>
+      <c r="A102" t="n">
+        <v>301420</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -8992,15 +8790,13 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>301423</t>
-        </is>
+      <c r="A103" t="n">
+        <v>301423</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -9076,15 +8872,13 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>301607</t>
-        </is>
+      <c r="A104" t="n">
+        <v>301607</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -9160,15 +8954,13 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>301151</t>
-        </is>
+      <c r="A105" t="n">
+        <v>301151</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -9244,15 +9036,13 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>300292</t>
-        </is>
+      <c r="A106" t="n">
+        <v>300292</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -9328,15 +9118,13 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>301110</t>
-        </is>
+      <c r="A107" t="n">
+        <v>301110</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -9412,15 +9200,13 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>301162</t>
-        </is>
+      <c r="A108" t="n">
+        <v>301162</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -9496,15 +9282,13 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>301175</t>
-        </is>
+      <c r="A109" t="n">
+        <v>301175</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -9580,15 +9364,13 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>301333</t>
-        </is>
+      <c r="A110" t="n">
+        <v>301333</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -9664,15 +9446,13 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>301592</t>
-        </is>
+      <c r="A111" t="n">
+        <v>301592</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -9748,15 +9528,13 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>301596</t>
-        </is>
+      <c r="A112" t="n">
+        <v>301596</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -9832,15 +9610,13 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>301610</t>
-        </is>
+      <c r="A113" t="n">
+        <v>301610</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -9916,15 +9692,13 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>301244</t>
-        </is>
+      <c r="A114" t="n">
+        <v>301244</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -10000,15 +9774,13 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>301623</t>
-        </is>
+      <c r="A115" t="n">
+        <v>301623</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -10084,15 +9856,13 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>301114</t>
-        </is>
+      <c r="A116" t="n">
+        <v>301114</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -10168,15 +9938,13 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>301247</t>
-        </is>
+      <c r="A117" t="n">
+        <v>301247</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -10252,15 +10020,13 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>301343</t>
-        </is>
+      <c r="A118" t="n">
+        <v>301343</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -10336,15 +10102,13 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>301390</t>
-        </is>
+      <c r="A119" t="n">
+        <v>301390</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -10420,15 +10184,13 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>301599</t>
-        </is>
+      <c r="A120" t="n">
+        <v>301599</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -10504,15 +10266,13 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>301687</t>
-        </is>
+      <c r="A121" t="n">
+        <v>301687</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -10588,15 +10348,13 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>301690</t>
-        </is>
+      <c r="A122" t="n">
+        <v>301690</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -10672,15 +10430,13 @@
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>301706</t>
-        </is>
+      <c r="A123" t="n">
+        <v>301706</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -10756,15 +10512,13 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>301240</t>
-        </is>
+      <c r="A124" t="n">
+        <v>301240</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -10840,15 +10594,13 @@
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>301435</t>
-        </is>
+      <c r="A125" t="n">
+        <v>301435</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -10924,15 +10676,13 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>301551</t>
-        </is>
+      <c r="A126" t="n">
+        <v>301551</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -11008,15 +10758,13 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>301581</t>
-        </is>
+      <c r="A127" t="n">
+        <v>301581</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -11092,15 +10840,13 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>301584</t>
-        </is>
+      <c r="A128" t="n">
+        <v>301584</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -11176,15 +10922,13 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>301616</t>
-        </is>
+      <c r="A129" t="n">
+        <v>301616</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -11260,15 +11004,13 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>301642</t>
-        </is>
+      <c r="A130" t="n">
+        <v>301642</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -11344,15 +11086,13 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>301861</t>
-        </is>
+      <c r="A131" t="n">
+        <v>301861</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -11428,15 +11168,13 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>301498</t>
-        </is>
+      <c r="A132" t="n">
+        <v>301498</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -11512,15 +11250,13 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>301500</t>
-        </is>
+      <c r="A133" t="n">
+        <v>301500</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -11596,15 +11332,13 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>301825</t>
-        </is>
+      <c r="A134" t="n">
+        <v>301825</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -11680,15 +11414,13 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>301349</t>
-        </is>
+      <c r="A135" t="n">
+        <v>301349</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -11764,15 +11496,13 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>301456</t>
-        </is>
+      <c r="A136" t="n">
+        <v>301456</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -11848,15 +11578,13 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>301505</t>
-        </is>
+      <c r="A137" t="n">
+        <v>301505</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -11932,15 +11660,13 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>301643</t>
-        </is>
+      <c r="A138" t="n">
+        <v>301643</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -12016,15 +11742,13 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>301646</t>
-        </is>
+      <c r="A139" t="n">
+        <v>301646</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -12100,15 +11824,13 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>301748</t>
-        </is>
+      <c r="A140" t="n">
+        <v>301748</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -12184,15 +11906,13 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>301828</t>
-        </is>
+      <c r="A141" t="n">
+        <v>301828</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -12268,15 +11988,13 @@
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>301494</t>
-        </is>
+      <c r="A142" t="n">
+        <v>301494</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -12352,15 +12070,13 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>301510</t>
-        </is>
+      <c r="A143" t="n">
+        <v>301510</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -12436,15 +12152,13 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>301777</t>
-        </is>
+      <c r="A144" t="n">
+        <v>301777</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -12520,15 +12234,13 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>300323</t>
-        </is>
+      <c r="A145" t="n">
+        <v>300323</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -12604,15 +12316,13 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>301375</t>
-        </is>
+      <c r="A146" t="n">
+        <v>301375</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -12688,15 +12398,13 @@
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>301459</t>
-        </is>
+      <c r="A147" t="n">
+        <v>301459</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -12772,15 +12480,13 @@
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>301480</t>
-        </is>
+      <c r="A148" t="n">
+        <v>301480</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -12856,15 +12562,13 @@
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>301754</t>
-        </is>
+      <c r="A149" t="n">
+        <v>301754</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -12940,15 +12644,13 @@
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>301780</t>
-        </is>
+      <c r="A150" t="n">
+        <v>301780</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -13024,15 +12726,13 @@
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>301991</t>
-        </is>
+      <c r="A151" t="n">
+        <v>301991</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -13108,15 +12808,13 @@
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>301878</t>
-        </is>
+      <c r="A152" t="n">
+        <v>301878</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -13192,15 +12890,13 @@
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>301518</t>
-        </is>
+      <c r="A153" t="n">
+        <v>301518</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -13276,15 +12972,13 @@
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>301520</t>
-        </is>
+      <c r="A154" t="n">
+        <v>301520</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -13360,15 +13054,13 @@
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>301657</t>
-        </is>
+      <c r="A155" t="n">
+        <v>301657</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -13444,15 +13136,13 @@
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>301441</t>
-        </is>
+      <c r="A156" t="n">
+        <v>301441</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -13528,15 +13218,13 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>301525</t>
-        </is>
+      <c r="A157" t="n">
+        <v>301525</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -13612,15 +13300,13 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>301612</t>
-        </is>
+      <c r="A158" t="n">
+        <v>301612</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -13696,15 +13382,13 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>301614</t>
-        </is>
+      <c r="A159" t="n">
+        <v>301614</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -13780,15 +13464,13 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>301671</t>
-        </is>
+      <c r="A160" t="n">
+        <v>301671</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -13864,15 +13546,13 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>301773</t>
-        </is>
+      <c r="A161" t="n">
+        <v>301773</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -13948,15 +13628,13 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>301786</t>
-        </is>
+      <c r="A162" t="n">
+        <v>301786</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -14032,15 +13710,13 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>302036</t>
-        </is>
+      <c r="A163" t="n">
+        <v>302036</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -14116,15 +13792,13 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>301789</t>
-        </is>
+      <c r="A164" t="n">
+        <v>301789</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -14200,15 +13874,13 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>301306</t>
-        </is>
+      <c r="A165" t="n">
+        <v>301306</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -14284,15 +13956,13 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>301444</t>
-        </is>
+      <c r="A166" t="n">
+        <v>301444</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -14368,15 +14038,13 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>301447</t>
-        </is>
+      <c r="A167" t="n">
+        <v>301447</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -14452,15 +14120,13 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>301553</t>
-        </is>
+      <c r="A168" t="n">
+        <v>301553</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -14536,15 +14202,13 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>301768</t>
-        </is>
+      <c r="A169" t="n">
+        <v>301768</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -14620,15 +14284,13 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>301774</t>
-        </is>
+      <c r="A170" t="n">
+        <v>301774</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -14704,15 +14366,13 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>301900</t>
-        </is>
+      <c r="A171" t="n">
+        <v>301900</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -14788,15 +14448,13 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>301901</t>
-        </is>
+      <c r="A172" t="n">
+        <v>301901</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -14872,15 +14530,13 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>301530</t>
-        </is>
+      <c r="A173" t="n">
+        <v>301530</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -14956,15 +14612,13 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>301532</t>
-        </is>
+      <c r="A174" t="n">
+        <v>301532</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -15040,15 +14694,13 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>301984</t>
-        </is>
+      <c r="A175" t="n">
+        <v>301984</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -15124,15 +14776,13 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>301453</t>
-        </is>
+      <c r="A176" t="n">
+        <v>301453</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -15208,15 +14858,13 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>301537</t>
-        </is>
+      <c r="A177" t="n">
+        <v>301537</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -15292,15 +14940,13 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>301566</t>
-        </is>
+      <c r="A178" t="n">
+        <v>301566</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -15376,15 +15022,13 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>301977</t>
-        </is>
+      <c r="A179" t="n">
+        <v>301977</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -15460,15 +15104,13 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>302019</t>
-        </is>
+      <c r="A180" t="n">
+        <v>302019</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -15544,15 +15186,13 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>302114</t>
-        </is>
+      <c r="A181" t="n">
+        <v>302114</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -15628,15 +15268,13 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>301814</t>
-        </is>
+      <c r="A182" t="n">
+        <v>301814</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -15712,15 +15350,13 @@
       </c>
       <c r="R182" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>301542</t>
-        </is>
+      <c r="A183" t="n">
+        <v>301542</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -15796,15 +15432,13 @@
       </c>
       <c r="R183" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>301544</t>
-        </is>
+      <c r="A184" t="n">
+        <v>301544</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -15880,15 +15514,13 @@
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>302022</t>
-        </is>
+      <c r="A185" t="n">
+        <v>302022</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -15964,15 +15596,13 @@
       </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>301462</t>
-        </is>
+      <c r="A186" t="n">
+        <v>301462</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -16048,15 +15678,13 @@
       </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>301465</t>
-        </is>
+      <c r="A187" t="n">
+        <v>301465</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -16132,15 +15760,13 @@
       </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>301701</t>
-        </is>
+      <c r="A188" t="n">
+        <v>301701</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -16216,15 +15842,13 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>302044</t>
-        </is>
+      <c r="A189" t="n">
+        <v>302044</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -16300,15 +15924,13 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>302050</t>
-        </is>
+      <c r="A190" t="n">
+        <v>302050</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -16384,15 +16006,13 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>302218</t>
-        </is>
+      <c r="A191" t="n">
+        <v>302218</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -16468,15 +16088,13 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>302256</t>
-        </is>
+      <c r="A192" t="n">
+        <v>302256</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -16552,15 +16170,13 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>301674</t>
-        </is>
+      <c r="A193" t="n">
+        <v>301674</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -16636,15 +16252,13 @@
       </c>
       <c r="R193" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>301801</t>
-        </is>
+      <c r="A194" t="n">
+        <v>301801</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -16720,15 +16334,13 @@
       </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>301874</t>
-        </is>
+      <c r="A195" t="n">
+        <v>301874</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -16804,15 +16416,13 @@
       </c>
       <c r="R195" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>301471</t>
-        </is>
+      <c r="A196" t="n">
+        <v>301471</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -16888,15 +16498,13 @@
       </c>
       <c r="R196" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>302025</t>
-        </is>
+      <c r="A197" t="n">
+        <v>302025</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -16972,15 +16580,13 @@
       </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>302092</t>
-        </is>
+      <c r="A198" t="n">
+        <v>302092</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -17056,15 +16662,13 @@
       </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>302383</t>
-        </is>
+      <c r="A199" t="n">
+        <v>302383</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -17140,15 +16744,13 @@
       </c>
       <c r="R199" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>301934</t>
-        </is>
+      <c r="A200" t="n">
+        <v>301934</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -17224,15 +16826,13 @@
       </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>302030</t>
-        </is>
+      <c r="A201" t="n">
+        <v>302030</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -17308,15 +16908,13 @@
       </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>302032</t>
-        </is>
+      <c r="A202" t="n">
+        <v>302032</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -17392,15 +16990,13 @@
       </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>302067</t>
-        </is>
+      <c r="A203" t="n">
+        <v>302067</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -17476,15 +17072,13 @@
       </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>302070</t>
-        </is>
+      <c r="A204" t="n">
+        <v>302070</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -17560,15 +17154,13 @@
       </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>302072</t>
-        </is>
+      <c r="A205" t="n">
+        <v>302072</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -17644,15 +17236,13 @@
       </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>302169</t>
-        </is>
+      <c r="A206" t="n">
+        <v>302169</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -17728,15 +17318,13 @@
       </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>302194</t>
-        </is>
+      <c r="A207" t="n">
+        <v>302194</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -17812,15 +17400,13 @@
       </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>302260</t>
-        </is>
+      <c r="A208" t="n">
+        <v>302260</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -17896,15 +17482,13 @@
       </c>
       <c r="R208" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>302302</t>
-        </is>
+      <c r="A209" t="n">
+        <v>302302</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -17980,15 +17564,13 @@
       </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>302305</t>
-        </is>
+      <c r="A210" t="n">
+        <v>302305</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -18064,15 +17646,13 @@
       </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>302408</t>
-        </is>
+      <c r="A211" t="n">
+        <v>302408</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -18148,15 +17728,13 @@
       </c>
       <c r="R211" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>302410</t>
-        </is>
+      <c r="A212" t="n">
+        <v>302410</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -18232,15 +17810,13 @@
       </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>301486</t>
-        </is>
+      <c r="A213" t="n">
+        <v>301486</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -18316,15 +17892,13 @@
       </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>302445</t>
-        </is>
+      <c r="A214" t="n">
+        <v>302445</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -18400,15 +17974,13 @@
       </c>
       <c r="R214" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>301997</t>
-        </is>
+      <c r="A215" t="n">
+        <v>301997</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -18484,15 +18056,13 @@
       </c>
       <c r="R215" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>302310</t>
-        </is>
+      <c r="A216" t="n">
+        <v>302310</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -18568,15 +18138,13 @@
       </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>302313</t>
-        </is>
+      <c r="A217" t="n">
+        <v>302313</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -18652,15 +18220,13 @@
       </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>302482</t>
-        </is>
+      <c r="A218" t="n">
+        <v>302482</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -18736,15 +18302,13 @@
       </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>302076</t>
-        </is>
+      <c r="A219" t="n">
+        <v>302076</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -18820,15 +18384,13 @@
       </c>
       <c r="R219" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>302077</t>
-        </is>
+      <c r="A220" t="n">
+        <v>302077</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -18904,15 +18466,13 @@
       </c>
       <c r="R220" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>302081</t>
-        </is>
+      <c r="A221" t="n">
+        <v>302081</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -18988,15 +18548,13 @@
       </c>
       <c r="R221" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>302083</t>
-        </is>
+      <c r="A222" t="n">
+        <v>302083</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -19072,15 +18630,13 @@
       </c>
       <c r="R222" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>301767</t>
-        </is>
+      <c r="A223" t="n">
+        <v>301767</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -19156,15 +18712,13 @@
       </c>
       <c r="R223" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>302617</t>
-        </is>
+      <c r="A224" t="n">
+        <v>302617</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -19240,15 +18794,13 @@
       </c>
       <c r="R224" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>301969</t>
-        </is>
+      <c r="A225" t="n">
+        <v>301969</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -19324,15 +18876,13 @@
       </c>
       <c r="R225" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>302453</t>
-        </is>
+      <c r="A226" t="n">
+        <v>302453</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -19408,15 +18958,13 @@
       </c>
       <c r="R226" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>302332</t>
-        </is>
+      <c r="A227" t="n">
+        <v>302332</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -19492,15 +19040,13 @@
       </c>
       <c r="R227" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>302491</t>
-        </is>
+      <c r="A228" t="n">
+        <v>302491</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -19576,15 +19122,13 @@
       </c>
       <c r="R228" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>302635</t>
-        </is>
+      <c r="A229" t="n">
+        <v>302635</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -19660,15 +19204,13 @@
       </c>
       <c r="R229" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>302062</t>
-        </is>
+      <c r="A230" t="n">
+        <v>302062</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -19744,15 +19286,13 @@
       </c>
       <c r="R230" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>302434</t>
-        </is>
+      <c r="A231" t="n">
+        <v>302434</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -19828,15 +19368,13 @@
       </c>
       <c r="R231" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>302436</t>
-        </is>
+      <c r="A232" t="n">
+        <v>302436</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -19912,15 +19450,13 @@
       </c>
       <c r="R232" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>302494</t>
-        </is>
+      <c r="A233" t="n">
+        <v>302494</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -19996,15 +19532,13 @@
       </c>
       <c r="R233" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>302541</t>
-        </is>
+      <c r="A234" t="n">
+        <v>302541</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -20080,15 +19614,13 @@
       </c>
       <c r="R234" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>302545</t>
-        </is>
+      <c r="A235" t="n">
+        <v>302545</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -20164,15 +19696,13 @@
       </c>
       <c r="R235" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>302639</t>
-        </is>
+      <c r="A236" t="n">
+        <v>302639</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -20248,15 +19778,13 @@
       </c>
       <c r="R236" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>302692</t>
-        </is>
+      <c r="A237" t="n">
+        <v>302692</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -20332,15 +19860,13 @@
       </c>
       <c r="R237" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>302717</t>
-        </is>
+      <c r="A238" t="n">
+        <v>302717</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -20416,15 +19942,13 @@
       </c>
       <c r="R238" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>302550</t>
-        </is>
+      <c r="A239" t="n">
+        <v>302550</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -20500,15 +20024,13 @@
       </c>
       <c r="R239" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>302554</t>
-        </is>
+      <c r="A240" t="n">
+        <v>302554</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -20584,15 +20106,13 @@
       </c>
       <c r="R240" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>302518</t>
-        </is>
+      <c r="A241" t="n">
+        <v>302518</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
@@ -20668,15 +20188,13 @@
       </c>
       <c r="R241" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>302773</t>
-        </is>
+      <c r="A242" t="n">
+        <v>302773</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
@@ -20752,15 +20270,13 @@
       </c>
       <c r="R242" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>302212</t>
-        </is>
+      <c r="A243" t="n">
+        <v>302212</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
@@ -20836,15 +20352,13 @@
       </c>
       <c r="R243" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>302624</t>
-        </is>
+      <c r="A244" t="n">
+        <v>302624</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
@@ -20920,15 +20434,13 @@
       </c>
       <c r="R244" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>302777</t>
-        </is>
+      <c r="A245" t="n">
+        <v>302777</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
@@ -21004,15 +20516,13 @@
       </c>
       <c r="R245" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>302807</t>
-        </is>
+      <c r="A246" t="n">
+        <v>302807</v>
       </c>
       <c r="B246" t="inlineStr">
         <is>
@@ -21088,15 +20598,13 @@
       </c>
       <c r="R246" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>302809</t>
-        </is>
+      <c r="A247" t="n">
+        <v>302809</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
@@ -21172,15 +20680,13 @@
       </c>
       <c r="R247" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>302811</t>
-        </is>
+      <c r="A248" t="n">
+        <v>302811</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
@@ -21256,15 +20762,13 @@
       </c>
       <c r="R248" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>302704</t>
-        </is>
+      <c r="A249" t="n">
+        <v>302704</v>
       </c>
       <c r="B249" t="inlineStr">
         <is>
@@ -21340,15 +20844,13 @@
       </c>
       <c r="R249" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>302746</t>
-        </is>
+      <c r="A250" t="n">
+        <v>302746</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
@@ -21424,15 +20926,13 @@
       </c>
       <c r="R250" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>302757</t>
-        </is>
+      <c r="A251" t="n">
+        <v>302757</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
@@ -21508,15 +21008,13 @@
       </c>
       <c r="R251" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>302817</t>
-        </is>
+      <c r="A252" t="n">
+        <v>302817</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
@@ -21592,15 +21090,13 @@
       </c>
       <c r="R252" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>302658</t>
-        </is>
+      <c r="A253" t="n">
+        <v>302658</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
@@ -21676,15 +21172,13 @@
       </c>
       <c r="R253" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>302660</t>
-        </is>
+      <c r="A254" t="n">
+        <v>302660</v>
       </c>
       <c r="B254" t="inlineStr">
         <is>
@@ -21760,15 +21254,13 @@
       </c>
       <c r="R254" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>302822</t>
-        </is>
+      <c r="A255" t="n">
+        <v>302822</v>
       </c>
       <c r="B255" t="inlineStr">
         <is>
@@ -21844,15 +21336,13 @@
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>302665</t>
-        </is>
+      <c r="A256" t="n">
+        <v>302665</v>
       </c>
       <c r="B256" t="inlineStr">
         <is>
@@ -21928,15 +21418,13 @@
       </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>302669</t>
-        </is>
+      <c r="A257" t="n">
+        <v>302669</v>
       </c>
       <c r="B257" t="inlineStr">
         <is>
@@ -22012,15 +21500,13 @@
       </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>302707</t>
-        </is>
+      <c r="A258" t="n">
+        <v>302707</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
@@ -22096,15 +21582,13 @@
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>302747</t>
-        </is>
+      <c r="A259" t="n">
+        <v>302747</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -22180,15 +21664,13 @@
       </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>302820</t>
-        </is>
+      <c r="A260" t="n">
+        <v>302820</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -22264,15 +21746,13 @@
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>303113</t>
-        </is>
+      <c r="A261" t="n">
+        <v>303113</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -22348,15 +21828,13 @@
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>302670</t>
-        </is>
+      <c r="A262" t="n">
+        <v>302670</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -22432,15 +21910,13 @@
       </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>303109</t>
-        </is>
+      <c r="A263" t="n">
+        <v>303109</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -22516,15 +21992,13 @@
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>302615</t>
-        </is>
+      <c r="A264" t="n">
+        <v>302615</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -22600,15 +22074,13 @@
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>302844</t>
-        </is>
+      <c r="A265" t="n">
+        <v>302844</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -22684,15 +22156,13 @@
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>302942</t>
-        </is>
+      <c r="A266" t="n">
+        <v>302942</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -22768,15 +22238,13 @@
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>302946</t>
-        </is>
+      <c r="A267" t="n">
+        <v>302946</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -22852,15 +22320,13 @@
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>303039</t>
-        </is>
+      <c r="A268" t="n">
+        <v>303039</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -22936,15 +22402,13 @@
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>302956</t>
-        </is>
+      <c r="A269" t="n">
+        <v>302956</v>
       </c>
       <c r="B269" t="inlineStr">
         <is>
@@ -23020,15 +22484,13 @@
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>303090</t>
-        </is>
+      <c r="A270" t="n">
+        <v>303090</v>
       </c>
       <c r="B270" t="inlineStr">
         <is>
@@ -23104,15 +22566,13 @@
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>303127</t>
-        </is>
+      <c r="A271" t="n">
+        <v>303127</v>
       </c>
       <c r="B271" t="inlineStr">
         <is>
@@ -23188,15 +22648,13 @@
       </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>303134</t>
-        </is>
+      <c r="A272" t="n">
+        <v>303134</v>
       </c>
       <c r="B272" t="inlineStr">
         <is>
@@ -23272,15 +22730,13 @@
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>303135</t>
-        </is>
+      <c r="A273" t="n">
+        <v>303135</v>
       </c>
       <c r="B273" t="inlineStr">
         <is>
@@ -23356,15 +22812,13 @@
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>303169</t>
-        </is>
+      <c r="A274" t="n">
+        <v>303169</v>
       </c>
       <c r="B274" t="inlineStr">
         <is>
@@ -23440,15 +22894,13 @@
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>302901</t>
-        </is>
+      <c r="A275" t="n">
+        <v>302901</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
@@ -23524,15 +22976,13 @@
       </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>302797</t>
-        </is>
+      <c r="A276" t="n">
+        <v>302797</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
@@ -23608,15 +23058,13 @@
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>302912</t>
-        </is>
+      <c r="A277" t="n">
+        <v>302912</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
@@ -23692,15 +23140,13 @@
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>303093</t>
-        </is>
+      <c r="A278" t="n">
+        <v>303093</v>
       </c>
       <c r="B278" t="inlineStr">
         <is>
@@ -23776,15 +23222,13 @@
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>303131</t>
-        </is>
+      <c r="A279" t="n">
+        <v>303131</v>
       </c>
       <c r="B279" t="inlineStr">
         <is>
@@ -23860,15 +23304,13 @@
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>303184</t>
-        </is>
+      <c r="A280" t="n">
+        <v>303184</v>
       </c>
       <c r="B280" t="inlineStr">
         <is>
@@ -23944,15 +23386,13 @@
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>302598</t>
-        </is>
+      <c r="A281" t="n">
+        <v>302598</v>
       </c>
       <c r="B281" t="inlineStr">
         <is>
@@ -24028,15 +23468,13 @@
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>303187</t>
-        </is>
+      <c r="A282" t="n">
+        <v>303187</v>
       </c>
       <c r="B282" t="inlineStr">
         <is>
@@ -24112,15 +23550,13 @@
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>302587</t>
-        </is>
+      <c r="A283" t="n">
+        <v>302587</v>
       </c>
       <c r="B283" t="inlineStr">
         <is>
@@ -24196,15 +23632,13 @@
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>302645</t>
-        </is>
+      <c r="A284" t="n">
+        <v>302645</v>
       </c>
       <c r="B284" t="inlineStr">
         <is>
@@ -24280,15 +23714,13 @@
       </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>302766</t>
-        </is>
+      <c r="A285" t="n">
+        <v>302766</v>
       </c>
       <c r="B285" t="inlineStr">
         <is>
@@ -24364,15 +23796,13 @@
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="inlineStr">
-        <is>
-          <t>302872</t>
-        </is>
+      <c r="A286" t="n">
+        <v>302872</v>
       </c>
       <c r="B286" t="inlineStr">
         <is>
@@ -24448,15 +23878,13 @@
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>303096</t>
-        </is>
+      <c r="A287" t="n">
+        <v>303096</v>
       </c>
       <c r="B287" t="inlineStr">
         <is>
@@ -24532,15 +23960,13 @@
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>303137</t>
-        </is>
+      <c r="A288" t="n">
+        <v>303137</v>
       </c>
       <c r="B288" t="inlineStr">
         <is>
@@ -24616,15 +24042,13 @@
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>303139</t>
-        </is>
+      <c r="A289" t="n">
+        <v>303139</v>
       </c>
       <c r="B289" t="inlineStr">
         <is>
@@ -24700,15 +24124,13 @@
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>303179</t>
-        </is>
+      <c r="A290" t="n">
+        <v>303179</v>
       </c>
       <c r="B290" t="inlineStr">
         <is>
@@ -24784,15 +24206,13 @@
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="inlineStr">
-        <is>
-          <t>303118</t>
-        </is>
+      <c r="A291" t="n">
+        <v>303118</v>
       </c>
       <c r="B291" t="inlineStr">
         <is>
@@ -24868,15 +24288,13 @@
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="inlineStr">
-        <is>
-          <t>303200</t>
-        </is>
+      <c r="A292" t="n">
+        <v>303200</v>
       </c>
       <c r="B292" t="inlineStr">
         <is>
@@ -24952,15 +24370,13 @@
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>303203</t>
-        </is>
+      <c r="A293" t="n">
+        <v>303203</v>
       </c>
       <c r="B293" t="inlineStr">
         <is>
@@ -25036,15 +24452,13 @@
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>303310</t>
-        </is>
+      <c r="A294" t="n">
+        <v>303310</v>
       </c>
       <c r="B294" t="inlineStr">
         <is>
@@ -25120,15 +24534,13 @@
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>302968</t>
-        </is>
+      <c r="A295" t="n">
+        <v>302968</v>
       </c>
       <c r="B295" t="inlineStr">
         <is>
@@ -25204,15 +24616,13 @@
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>302970</t>
-        </is>
+      <c r="A296" t="n">
+        <v>302970</v>
       </c>
       <c r="B296" t="inlineStr">
         <is>
@@ -25288,15 +24698,13 @@
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>302975</t>
-        </is>
+      <c r="A297" t="n">
+        <v>302975</v>
       </c>
       <c r="B297" t="inlineStr">
         <is>
@@ -25372,15 +24780,13 @@
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>302979</t>
-        </is>
+      <c r="A298" t="n">
+        <v>302979</v>
       </c>
       <c r="B298" t="inlineStr">
         <is>
@@ -25456,15 +24862,13 @@
       </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>303143</t>
-        </is>
+      <c r="A299" t="n">
+        <v>303143</v>
       </c>
       <c r="B299" t="inlineStr">
         <is>
@@ -25540,15 +24944,13 @@
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>303144</t>
-        </is>
+      <c r="A300" t="n">
+        <v>303144</v>
       </c>
       <c r="B300" t="inlineStr">
         <is>
@@ -25624,15 +25026,13 @@
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>303001</t>
-        </is>
+      <c r="A301" t="n">
+        <v>303001</v>
       </c>
       <c r="B301" t="inlineStr">
         <is>
@@ -25708,15 +25108,13 @@
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>303003</t>
-        </is>
+      <c r="A302" t="n">
+        <v>303003</v>
       </c>
       <c r="B302" t="inlineStr">
         <is>
@@ -25792,15 +25190,13 @@
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>303317</t>
-        </is>
+      <c r="A303" t="n">
+        <v>303317</v>
       </c>
       <c r="B303" t="inlineStr">
         <is>
@@ -25876,15 +25272,13 @@
       </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>303016</t>
-        </is>
+      <c r="A304" t="n">
+        <v>303016</v>
       </c>
       <c r="B304" t="inlineStr">
         <is>
@@ -25960,15 +25354,13 @@
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>303020</t>
-        </is>
+      <c r="A305" t="n">
+        <v>303020</v>
       </c>
       <c r="B305" t="inlineStr">
         <is>
@@ -26044,15 +25436,13 @@
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>303153</t>
-        </is>
+      <c r="A306" t="n">
+        <v>303153</v>
       </c>
       <c r="B306" t="inlineStr">
         <is>
@@ -26128,15 +25518,13 @@
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>303242</t>
-        </is>
+      <c r="A307" t="n">
+        <v>303242</v>
       </c>
       <c r="B307" t="inlineStr">
         <is>
@@ -26212,15 +25600,13 @@
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>303322</t>
-        </is>
+      <c r="A308" t="n">
+        <v>303322</v>
       </c>
       <c r="B308" t="inlineStr">
         <is>
@@ -26296,15 +25682,13 @@
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>303059</t>
-        </is>
+      <c r="A309" t="n">
+        <v>303059</v>
       </c>
       <c r="B309" t="inlineStr">
         <is>
@@ -26380,15 +25764,13 @@
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>303061</t>
-        </is>
+      <c r="A310" t="n">
+        <v>303061</v>
       </c>
       <c r="B310" t="inlineStr">
         <is>
@@ -26464,15 +25846,13 @@
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="inlineStr">
-        <is>
-          <t>303122</t>
-        </is>
+      <c r="A311" t="n">
+        <v>303122</v>
       </c>
       <c r="B311" t="inlineStr">
         <is>
@@ -26548,15 +25928,13 @@
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="inlineStr">
-        <is>
-          <t>303154</t>
-        </is>
+      <c r="A312" t="n">
+        <v>303154</v>
       </c>
       <c r="B312" t="inlineStr">
         <is>
@@ -26632,15 +26010,13 @@
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>303158</t>
-        </is>
+      <c r="A313" t="n">
+        <v>303158</v>
       </c>
       <c r="B313" t="inlineStr">
         <is>
@@ -26716,15 +26092,13 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>303329</t>
-        </is>
+      <c r="A314" t="n">
+        <v>303329</v>
       </c>
       <c r="B314" t="inlineStr">
         <is>
@@ -26800,15 +26174,13 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>303085</t>
-        </is>
+      <c r="A315" t="n">
+        <v>303085</v>
       </c>
       <c r="B315" t="inlineStr">
         <is>
@@ -26884,15 +26256,13 @@
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>303370</t>
-        </is>
+      <c r="A316" t="n">
+        <v>303370</v>
       </c>
       <c r="B316" t="inlineStr">
         <is>
@@ -26968,15 +26338,13 @@
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>302839</t>
-        </is>
+      <c r="A317" t="n">
+        <v>302839</v>
       </c>
       <c r="B317" t="inlineStr">
         <is>
@@ -27052,15 +26420,13 @@
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>303278</t>
-        </is>
+      <c r="A318" t="n">
+        <v>303278</v>
       </c>
       <c r="B318" t="inlineStr">
         <is>
@@ -27136,15 +26502,13 @@
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>303335</t>
-        </is>
+      <c r="A319" t="n">
+        <v>303335</v>
       </c>
       <c r="B319" t="inlineStr">
         <is>
@@ -27220,15 +26584,13 @@
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>303378</t>
-        </is>
+      <c r="A320" t="n">
+        <v>303378</v>
       </c>
       <c r="B320" t="inlineStr">
         <is>
@@ -27304,15 +26666,13 @@
       </c>
       <c r="R320" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>303505</t>
-        </is>
+      <c r="A321" t="n">
+        <v>303505</v>
       </c>
       <c r="B321" t="inlineStr">
         <is>
@@ -27388,15 +26748,13 @@
       </c>
       <c r="R321" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>303568</t>
-        </is>
+      <c r="A322" t="n">
+        <v>303568</v>
       </c>
       <c r="B322" t="inlineStr">
         <is>
@@ -27472,15 +26830,13 @@
       </c>
       <c r="R322" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>303283</t>
-        </is>
+      <c r="A323" t="n">
+        <v>303283</v>
       </c>
       <c r="B323" t="inlineStr">
         <is>
@@ -27556,15 +26912,13 @@
       </c>
       <c r="R323" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>303285</t>
-        </is>
+      <c r="A324" t="n">
+        <v>303285</v>
       </c>
       <c r="B324" t="inlineStr">
         <is>
@@ -27640,15 +26994,13 @@
       </c>
       <c r="R324" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>303160</t>
-        </is>
+      <c r="A325" t="n">
+        <v>303160</v>
       </c>
       <c r="B325" t="inlineStr">
         <is>
@@ -27724,15 +27076,13 @@
       </c>
       <c r="R325" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>303162</t>
-        </is>
+      <c r="A326" t="n">
+        <v>303162</v>
       </c>
       <c r="B326" t="inlineStr">
         <is>
@@ -27808,15 +27158,13 @@
       </c>
       <c r="R326" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>303289</t>
-        </is>
+      <c r="A327" t="n">
+        <v>303289</v>
       </c>
       <c r="B327" t="inlineStr">
         <is>
@@ -27892,15 +27240,13 @@
       </c>
       <c r="R327" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>303293</t>
-        </is>
+      <c r="A328" t="n">
+        <v>303293</v>
       </c>
       <c r="B328" t="inlineStr">
         <is>
@@ -27976,15 +27322,13 @@
       </c>
       <c r="R328" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>303346</t>
-        </is>
+      <c r="A329" t="n">
+        <v>303346</v>
       </c>
       <c r="B329" t="inlineStr">
         <is>
@@ -28060,15 +27404,13 @@
       </c>
       <c r="R329" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>303412</t>
-        </is>
+      <c r="A330" t="n">
+        <v>303412</v>
       </c>
       <c r="B330" t="inlineStr">
         <is>
@@ -28144,15 +27486,13 @@
       </c>
       <c r="R330" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>303572</t>
-        </is>
+      <c r="A331" t="n">
+        <v>303572</v>
       </c>
       <c r="B331" t="inlineStr">
         <is>
@@ -28228,15 +27568,13 @@
       </c>
       <c r="R331" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>303385</t>
-        </is>
+      <c r="A332" t="n">
+        <v>303385</v>
       </c>
       <c r="B332" t="inlineStr">
         <is>
@@ -28312,15 +27650,13 @@
       </c>
       <c r="R332" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>303386</t>
-        </is>
+      <c r="A333" t="n">
+        <v>303386</v>
       </c>
       <c r="B333" t="inlineStr">
         <is>
@@ -28396,15 +27732,13 @@
       </c>
       <c r="R333" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>303395</t>
-        </is>
+      <c r="A334" t="n">
+        <v>303395</v>
       </c>
       <c r="B334" t="inlineStr">
         <is>
@@ -28480,15 +27814,13 @@
       </c>
       <c r="R334" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>303417</t>
-        </is>
+      <c r="A335" t="n">
+        <v>303417</v>
       </c>
       <c r="B335" t="inlineStr">
         <is>
@@ -28564,15 +27896,13 @@
       </c>
       <c r="R335" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>303419</t>
-        </is>
+      <c r="A336" t="n">
+        <v>303419</v>
       </c>
       <c r="B336" t="inlineStr">
         <is>
@@ -28648,15 +27978,13 @@
       </c>
       <c r="R336" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>303592</t>
-        </is>
+      <c r="A337" t="n">
+        <v>303592</v>
       </c>
       <c r="B337" t="inlineStr">
         <is>
@@ -28732,15 +28060,13 @@
       </c>
       <c r="R337" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>303571</t>
-        </is>
+      <c r="A338" t="n">
+        <v>303571</v>
       </c>
       <c r="B338" t="inlineStr">
         <is>
@@ -28816,15 +28142,13 @@
       </c>
       <c r="R338" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>303599</t>
-        </is>
+      <c r="A339" t="n">
+        <v>303599</v>
       </c>
       <c r="B339" t="inlineStr">
         <is>
@@ -28900,15 +28224,13 @@
       </c>
       <c r="R339" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>303610</t>
-        </is>
+      <c r="A340" t="n">
+        <v>303610</v>
       </c>
       <c r="B340" t="inlineStr">
         <is>
@@ -28984,15 +28306,13 @@
       </c>
       <c r="R340" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>303622</t>
-        </is>
+      <c r="A341" t="n">
+        <v>303622</v>
       </c>
       <c r="B341" t="inlineStr">
         <is>
@@ -29068,15 +28388,13 @@
       </c>
       <c r="R341" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>303539</t>
-        </is>
+      <c r="A342" t="n">
+        <v>303539</v>
       </c>
       <c r="B342" t="inlineStr">
         <is>
@@ -29152,15 +28470,13 @@
       </c>
       <c r="R342" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>303549</t>
-        </is>
+      <c r="A343" t="n">
+        <v>303549</v>
       </c>
       <c r="B343" t="inlineStr">
         <is>
@@ -29236,15 +28552,13 @@
       </c>
       <c r="R343" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>303553</t>
-        </is>
+      <c r="A344" t="n">
+        <v>303553</v>
       </c>
       <c r="B344" t="inlineStr">
         <is>
@@ -29320,15 +28634,13 @@
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>303555</t>
-        </is>
+      <c r="A345" t="n">
+        <v>303555</v>
       </c>
       <c r="B345" t="inlineStr">
         <is>
@@ -29404,15 +28716,13 @@
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>303557</t>
-        </is>
+      <c r="A346" t="n">
+        <v>303557</v>
       </c>
       <c r="B346" t="inlineStr">
         <is>
@@ -29488,15 +28798,13 @@
       </c>
       <c r="R346" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>303631</t>
-        </is>
+      <c r="A347" t="n">
+        <v>303631</v>
       </c>
       <c r="B347" t="inlineStr">
         <is>
@@ -29572,15 +28880,13 @@
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>303675</t>
-        </is>
+      <c r="A348" t="n">
+        <v>303675</v>
       </c>
       <c r="B348" t="inlineStr">
         <is>
@@ -29656,15 +28962,13 @@
       </c>
       <c r="R348" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>303559</t>
-        </is>
+      <c r="A349" t="n">
+        <v>303559</v>
       </c>
       <c r="B349" t="inlineStr">
         <is>
@@ -29740,15 +29044,13 @@
       </c>
       <c r="R349" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>303640</t>
-        </is>
+      <c r="A350" t="n">
+        <v>303640</v>
       </c>
       <c r="B350" t="inlineStr">
         <is>
@@ -29824,15 +29126,13 @@
       </c>
       <c r="R350" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>303489</t>
-        </is>
+      <c r="A351" t="n">
+        <v>303489</v>
       </c>
       <c r="B351" t="inlineStr">
         <is>
@@ -29908,15 +29208,13 @@
       </c>
       <c r="R351" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>303491</t>
-        </is>
+      <c r="A352" t="n">
+        <v>303491</v>
       </c>
       <c r="B352" t="inlineStr">
         <is>
@@ -29992,15 +29290,13 @@
       </c>
       <c r="R352" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>303512</t>
-        </is>
+      <c r="A353" t="n">
+        <v>303512</v>
       </c>
       <c r="B353" t="inlineStr">
         <is>
@@ -30076,15 +29372,13 @@
       </c>
       <c r="R353" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>303522</t>
-        </is>
+      <c r="A354" t="n">
+        <v>303522</v>
       </c>
       <c r="B354" t="inlineStr">
         <is>
@@ -30160,15 +29454,13 @@
       </c>
       <c r="R354" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>303646</t>
-        </is>
+      <c r="A355" t="n">
+        <v>303646</v>
       </c>
       <c r="B355" t="inlineStr">
         <is>
@@ -30244,15 +29536,13 @@
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>303648</t>
-        </is>
+      <c r="A356" t="n">
+        <v>303648</v>
       </c>
       <c r="B356" t="inlineStr">
         <is>
@@ -30328,15 +29618,13 @@
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>303650</t>
-        </is>
+      <c r="A357" t="n">
+        <v>303650</v>
       </c>
       <c r="B357" t="inlineStr">
         <is>
@@ -30412,15 +29700,13 @@
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>303683</t>
-        </is>
+      <c r="A358" t="n">
+        <v>303683</v>
       </c>
       <c r="B358" t="inlineStr">
         <is>
@@ -30496,15 +29782,13 @@
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>303699</t>
-        </is>
+      <c r="A359" t="n">
+        <v>303699</v>
       </c>
       <c r="B359" t="inlineStr">
         <is>
@@ -30580,15 +29864,13 @@
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>303602</t>
-        </is>
+      <c r="A360" t="n">
+        <v>303602</v>
       </c>
       <c r="B360" t="inlineStr">
         <is>
@@ -30664,15 +29946,13 @@
       </c>
       <c r="R360" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>303655</t>
-        </is>
+      <c r="A361" t="n">
+        <v>303655</v>
       </c>
       <c r="B361" t="inlineStr">
         <is>
@@ -30748,15 +30028,13 @@
       </c>
       <c r="R361" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>303659</t>
-        </is>
+      <c r="A362" t="n">
+        <v>303659</v>
       </c>
       <c r="B362" t="inlineStr">
         <is>
@@ -30832,15 +30110,13 @@
       </c>
       <c r="R362" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>303728</t>
-        </is>
+      <c r="A363" t="n">
+        <v>303728</v>
       </c>
       <c r="B363" t="inlineStr">
         <is>
@@ -30916,15 +30192,13 @@
       </c>
       <c r="R363" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>303743</t>
-        </is>
+      <c r="A364" t="n">
+        <v>303743</v>
       </c>
       <c r="B364" t="inlineStr">
         <is>
@@ -31000,15 +30274,13 @@
       </c>
       <c r="R364" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>303733</t>
-        </is>
+      <c r="A365" t="n">
+        <v>303733</v>
       </c>
       <c r="B365" t="inlineStr">
         <is>
@@ -31084,15 +30356,13 @@
       </c>
       <c r="R365" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="inlineStr">
-        <is>
-          <t>303741</t>
-        </is>
+      <c r="A366" t="n">
+        <v>303741</v>
       </c>
       <c r="B366" t="inlineStr">
         <is>
@@ -31168,15 +30438,13 @@
       </c>
       <c r="R366" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="inlineStr">
-        <is>
-          <t>303745</t>
-        </is>
+      <c r="A367" t="n">
+        <v>303745</v>
       </c>
       <c r="B367" t="inlineStr">
         <is>
@@ -31252,15 +30520,13 @@
       </c>
       <c r="R367" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>303797</t>
-        </is>
+      <c r="A368" t="n">
+        <v>303797</v>
       </c>
       <c r="B368" t="inlineStr">
         <is>
@@ -31336,15 +30602,13 @@
       </c>
       <c r="R368" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>303856</t>
-        </is>
+      <c r="A369" t="n">
+        <v>303856</v>
       </c>
       <c r="B369" t="inlineStr">
         <is>
@@ -31420,15 +30684,13 @@
       </c>
       <c r="R369" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>303618</t>
-        </is>
+      <c r="A370" t="n">
+        <v>303618</v>
       </c>
       <c r="B370" t="inlineStr">
         <is>
@@ -31504,15 +30766,13 @@
       </c>
       <c r="R370" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>303765</t>
-        </is>
+      <c r="A371" t="n">
+        <v>303765</v>
       </c>
       <c r="B371" t="inlineStr">
         <is>
@@ -31588,15 +30848,13 @@
       </c>
       <c r="R371" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>303816</t>
-        </is>
+      <c r="A372" t="n">
+        <v>303816</v>
       </c>
       <c r="B372" t="inlineStr">
         <is>
@@ -31672,15 +30930,13 @@
       </c>
       <c r="R372" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>303845</t>
-        </is>
+      <c r="A373" t="n">
+        <v>303845</v>
       </c>
       <c r="B373" t="inlineStr">
         <is>
@@ -31756,15 +31012,13 @@
       </c>
       <c r="R373" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>304048</t>
-        </is>
+      <c r="A374" t="n">
+        <v>304048</v>
       </c>
       <c r="B374" t="inlineStr">
         <is>
@@ -31840,15 +31094,13 @@
       </c>
       <c r="R374" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>304050</t>
-        </is>
+      <c r="A375" t="n">
+        <v>304050</v>
       </c>
       <c r="B375" t="inlineStr">
         <is>
@@ -31924,15 +31176,13 @@
       </c>
       <c r="R375" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>303720</t>
-        </is>
+      <c r="A376" t="n">
+        <v>303720</v>
       </c>
       <c r="B376" t="inlineStr">
         <is>
@@ -32008,15 +31258,13 @@
       </c>
       <c r="R376" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>303776</t>
-        </is>
+      <c r="A377" t="n">
+        <v>303776</v>
       </c>
       <c r="B377" t="inlineStr">
         <is>
@@ -32092,15 +31340,13 @@
       </c>
       <c r="R377" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>303860</t>
-        </is>
+      <c r="A378" t="n">
+        <v>303860</v>
       </c>
       <c r="B378" t="inlineStr">
         <is>
@@ -32176,15 +31422,13 @@
       </c>
       <c r="R378" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>304099</t>
-        </is>
+      <c r="A379" t="n">
+        <v>304099</v>
       </c>
       <c r="B379" t="inlineStr">
         <is>
@@ -32260,15 +31504,13 @@
       </c>
       <c r="R379" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>304101</t>
-        </is>
+      <c r="A380" t="n">
+        <v>304101</v>
       </c>
       <c r="B380" t="inlineStr">
         <is>
@@ -32344,15 +31586,13 @@
       </c>
       <c r="R380" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>303781</t>
-        </is>
+      <c r="A381" t="n">
+        <v>303781</v>
       </c>
       <c r="B381" t="inlineStr">
         <is>
@@ -32428,15 +31668,13 @@
       </c>
       <c r="R381" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>303878</t>
-        </is>
+      <c r="A382" t="n">
+        <v>303878</v>
       </c>
       <c r="B382" t="inlineStr">
         <is>
@@ -32512,15 +31750,13 @@
       </c>
       <c r="R382" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>303786</t>
-        </is>
+      <c r="A383" t="n">
+        <v>303786</v>
       </c>
       <c r="B383" t="inlineStr">
         <is>
@@ -32596,15 +31832,13 @@
       </c>
       <c r="R383" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>303790</t>
-        </is>
+      <c r="A384" t="n">
+        <v>303790</v>
       </c>
       <c r="B384" t="inlineStr">
         <is>
@@ -32680,15 +31914,13 @@
       </c>
       <c r="R384" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>304081</t>
-        </is>
+      <c r="A385" t="n">
+        <v>304081</v>
       </c>
       <c r="B385" t="inlineStr">
         <is>
@@ -32764,15 +31996,13 @@
       </c>
       <c r="R385" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>304083</t>
-        </is>
+      <c r="A386" t="n">
+        <v>304083</v>
       </c>
       <c r="B386" t="inlineStr">
         <is>
@@ -32848,15 +32078,13 @@
       </c>
       <c r="R386" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>304179</t>
-        </is>
+      <c r="A387" t="n">
+        <v>304179</v>
       </c>
       <c r="B387" t="inlineStr">
         <is>
@@ -32932,15 +32160,13 @@
       </c>
       <c r="R387" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>304182</t>
-        </is>
+      <c r="A388" t="n">
+        <v>304182</v>
       </c>
       <c r="B388" t="inlineStr">
         <is>
@@ -33016,15 +32242,13 @@
       </c>
       <c r="R388" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>303893</t>
-        </is>
+      <c r="A389" t="n">
+        <v>303893</v>
       </c>
       <c r="B389" t="inlineStr">
         <is>
@@ -33100,15 +32324,13 @@
       </c>
       <c r="R389" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>304085</t>
-        </is>
+      <c r="A390" t="n">
+        <v>304085</v>
       </c>
       <c r="B390" t="inlineStr">
         <is>
@@ -33184,15 +32406,13 @@
       </c>
       <c r="R390" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>304261</t>
-        </is>
+      <c r="A391" t="n">
+        <v>304261</v>
       </c>
       <c r="B391" t="inlineStr">
         <is>
@@ -33268,15 +32488,13 @@
       </c>
       <c r="R391" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>304264</t>
-        </is>
+      <c r="A392" t="n">
+        <v>304264</v>
       </c>
       <c r="B392" t="inlineStr">
         <is>
@@ -33352,15 +32570,13 @@
       </c>
       <c r="R392" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>304281</t>
-        </is>
+      <c r="A393" t="n">
+        <v>304281</v>
       </c>
       <c r="B393" t="inlineStr">
         <is>
@@ -33436,15 +32652,13 @@
       </c>
       <c r="R393" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>304284</t>
-        </is>
+      <c r="A394" t="n">
+        <v>304284</v>
       </c>
       <c r="B394" t="inlineStr">
         <is>
@@ -33520,15 +32734,13 @@
       </c>
       <c r="R394" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>304510</t>
-        </is>
+      <c r="A395" t="n">
+        <v>304510</v>
       </c>
       <c r="B395" t="inlineStr">
         <is>
@@ -33604,15 +32816,13 @@
       </c>
       <c r="R395" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>304087</t>
-        </is>
+      <c r="A396" t="n">
+        <v>304087</v>
       </c>
       <c r="B396" t="inlineStr">
         <is>
@@ -33688,15 +32898,13 @@
       </c>
       <c r="R396" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>304089</t>
-        </is>
+      <c r="A397" t="n">
+        <v>304089</v>
       </c>
       <c r="B397" t="inlineStr">
         <is>
@@ -33772,15 +32980,13 @@
       </c>
       <c r="R397" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>303828</t>
-        </is>
+      <c r="A398" t="n">
+        <v>303828</v>
       </c>
       <c r="B398" t="inlineStr">
         <is>
@@ -33856,15 +33062,13 @@
       </c>
       <c r="R398" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>304210</t>
-        </is>
+      <c r="A399" t="n">
+        <v>304210</v>
       </c>
       <c r="B399" t="inlineStr">
         <is>
@@ -33940,15 +33144,13 @@
       </c>
       <c r="R399" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>304266</t>
-        </is>
+      <c r="A400" t="n">
+        <v>304266</v>
       </c>
       <c r="B400" t="inlineStr">
         <is>
@@ -34024,15 +33226,13 @@
       </c>
       <c r="R400" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>304339</t>
-        </is>
+      <c r="A401" t="n">
+        <v>304339</v>
       </c>
       <c r="B401" t="inlineStr">
         <is>
@@ -34108,15 +33308,13 @@
       </c>
       <c r="R401" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>303955</t>
-        </is>
+      <c r="A402" t="n">
+        <v>303955</v>
       </c>
       <c r="B402" t="inlineStr">
         <is>
@@ -34192,15 +33390,13 @@
       </c>
       <c r="R402" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>304034</t>
-        </is>
+      <c r="A403" t="n">
+        <v>304034</v>
       </c>
       <c r="B403" t="inlineStr">
         <is>
@@ -34276,15 +33472,13 @@
       </c>
       <c r="R403" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>304117</t>
-        </is>
+      <c r="A404" t="n">
+        <v>304117</v>
       </c>
       <c r="B404" t="inlineStr">
         <is>
@@ -34360,15 +33554,13 @@
       </c>
       <c r="R404" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>304121</t>
-        </is>
+      <c r="A405" t="n">
+        <v>304121</v>
       </c>
       <c r="B405" t="inlineStr">
         <is>
@@ -34444,15 +33636,13 @@
       </c>
       <c r="R405" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>304419</t>
-        </is>
+      <c r="A406" t="n">
+        <v>304419</v>
       </c>
       <c r="B406" t="inlineStr">
         <is>
@@ -34528,15 +33718,13 @@
       </c>
       <c r="R406" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>304430</t>
-        </is>
+      <c r="A407" t="n">
+        <v>304430</v>
       </c>
       <c r="B407" t="inlineStr">
         <is>
@@ -34612,15 +33800,13 @@
       </c>
       <c r="R407" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>304432</t>
-        </is>
+      <c r="A408" t="n">
+        <v>304432</v>
       </c>
       <c r="B408" t="inlineStr">
         <is>
@@ -34696,15 +33882,13 @@
       </c>
       <c r="R408" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>304148</t>
-        </is>
+      <c r="A409" t="n">
+        <v>304148</v>
       </c>
       <c r="B409" t="inlineStr">
         <is>
@@ -34780,15 +33964,13 @@
       </c>
       <c r="R409" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>304301</t>
-        </is>
+      <c r="A410" t="n">
+        <v>304301</v>
       </c>
       <c r="B410" t="inlineStr">
         <is>
@@ -34864,15 +34046,13 @@
       </c>
       <c r="R410" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>304194</t>
-        </is>
+      <c r="A411" t="n">
+        <v>304194</v>
       </c>
       <c r="B411" t="inlineStr">
         <is>
@@ -34948,15 +34128,13 @@
       </c>
       <c r="R411" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>304197</t>
-        </is>
+      <c r="A412" t="n">
+        <v>304197</v>
       </c>
       <c r="B412" t="inlineStr">
         <is>
@@ -35032,15 +34210,13 @@
       </c>
       <c r="R412" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>304296</t>
-        </is>
+      <c r="A413" t="n">
+        <v>304296</v>
       </c>
       <c r="B413" t="inlineStr">
         <is>
@@ -35116,15 +34292,13 @@
       </c>
       <c r="R413" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>304434</t>
-        </is>
+      <c r="A414" t="n">
+        <v>304434</v>
       </c>
       <c r="B414" t="inlineStr">
         <is>
@@ -35200,15 +34374,13 @@
       </c>
       <c r="R414" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>304437</t>
-        </is>
+      <c r="A415" t="n">
+        <v>304437</v>
       </c>
       <c r="B415" t="inlineStr">
         <is>
@@ -35284,15 +34456,13 @@
       </c>
       <c r="R415" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>304484</t>
-        </is>
+      <c r="A416" t="n">
+        <v>304484</v>
       </c>
       <c r="B416" t="inlineStr">
         <is>
@@ -35368,15 +34538,13 @@
       </c>
       <c r="R416" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>304470</t>
-        </is>
+      <c r="A417" t="n">
+        <v>304470</v>
       </c>
       <c r="B417" t="inlineStr">
         <is>
@@ -35452,15 +34620,13 @@
       </c>
       <c r="R417" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>304615</t>
-        </is>
+      <c r="A418" t="n">
+        <v>304615</v>
       </c>
       <c r="B418" t="inlineStr">
         <is>
@@ -35536,15 +34702,13 @@
       </c>
       <c r="R418" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>304322</t>
-        </is>
+      <c r="A419" t="n">
+        <v>304322</v>
       </c>
       <c r="B419" t="inlineStr">
         <is>
@@ -35620,15 +34784,13 @@
       </c>
       <c r="R419" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>304373</t>
-        </is>
+      <c r="A420" t="n">
+        <v>304373</v>
       </c>
       <c r="B420" t="inlineStr">
         <is>
@@ -35704,15 +34866,13 @@
       </c>
       <c r="R420" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>304475</t>
-        </is>
+      <c r="A421" t="n">
+        <v>304475</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
@@ -35788,15 +34948,13 @@
       </c>
       <c r="R421" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>304478</t>
-        </is>
+      <c r="A422" t="n">
+        <v>304478</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
@@ -35872,15 +35030,13 @@
       </c>
       <c r="R422" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>304550</t>
-        </is>
+      <c r="A423" t="n">
+        <v>304550</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
@@ -35956,15 +35112,13 @@
       </c>
       <c r="R423" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>304629</t>
-        </is>
+      <c r="A424" t="n">
+        <v>304629</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
@@ -36040,15 +35194,13 @@
       </c>
       <c r="R424" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>304630</t>
-        </is>
+      <c r="A425" t="n">
+        <v>304630</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
@@ -36124,15 +35276,13 @@
       </c>
       <c r="R425" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>304344</t>
-        </is>
+      <c r="A426" t="n">
+        <v>304344</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
@@ -36208,15 +35358,13 @@
       </c>
       <c r="R426" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>304056</t>
-        </is>
+      <c r="A427" t="n">
+        <v>304056</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
@@ -36292,15 +35440,13 @@
       </c>
       <c r="R427" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>304206</t>
-        </is>
+      <c r="A428" t="n">
+        <v>304206</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
@@ -36376,15 +35522,13 @@
       </c>
       <c r="R428" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>304445</t>
-        </is>
+      <c r="A429" t="n">
+        <v>304445</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
@@ -36460,15 +35604,13 @@
       </c>
       <c r="R429" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>304448</t>
-        </is>
+      <c r="A430" t="n">
+        <v>304448</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
@@ -36544,15 +35686,13 @@
       </c>
       <c r="R430" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>304641</t>
-        </is>
+      <c r="A431" t="n">
+        <v>304641</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
@@ -36628,7 +35768,7 @@
       </c>
       <c r="R431" t="inlineStr">
         <is>
-          <t>2026-05-11T18:50:51.955120+00:00</t>
+          <t>2026-05-11T20:10:55.611208+00:00</t>
         </is>
       </c>
     </row>

--- a/data/tournaments_master.xlsx
+++ b/data/tournaments_master.xlsx
@@ -585,7 +585,7 @@
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -837,7 +837,7 @@
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
       </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
       </c>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
       </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O89" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
       </c>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
       </c>
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
       </c>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="M103" t="inlineStr"/>
       <c r="N103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
       </c>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
       </c>
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
       </c>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
       </c>
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
       </c>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
       </c>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O117" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
       </c>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O118" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
       </c>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
       </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O122" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O123" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
       </c>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O126" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
@@ -11253,7 +11253,7 @@
       </c>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
       </c>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
       </c>
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
       </c>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
       </c>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -12093,7 +12093,7 @@
       </c>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
       </c>
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O140" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="M142" t="inlineStr"/>
       <c r="N142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
       </c>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
       </c>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
       </c>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
       </c>
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
       </c>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -13101,7 +13101,7 @@
       </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="M153" t="inlineStr"/>
       <c r="N153" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
       </c>
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="M156" t="inlineStr"/>
       <c r="N156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
       </c>
       <c r="M157" t="inlineStr"/>
       <c r="N157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
       </c>
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
       </c>
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
       </c>
       <c r="M161" t="inlineStr"/>
       <c r="N161" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
       </c>
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
       </c>
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
       </c>
       <c r="M166" t="inlineStr"/>
       <c r="N166" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -14445,7 +14445,7 @@
       </c>
       <c r="M167" t="inlineStr"/>
       <c r="N167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
       </c>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
       </c>
       <c r="M169" t="inlineStr"/>
       <c r="N169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O169" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
       </c>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O170" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
       </c>
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
       </c>
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
       </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
       </c>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
       </c>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O177" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
       </c>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O178" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
       </c>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O179" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O180" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O181" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
       </c>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O182" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
       </c>
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O183" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
       </c>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O184" t="inlineStr">
         <is>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="M185" t="inlineStr"/>
       <c r="N185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
       </c>
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O186" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
       </c>
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O187" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O188" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
       </c>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
       </c>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
@@ -16461,7 +16461,7 @@
       </c>
       <c r="M191" t="inlineStr"/>
       <c r="N191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O191" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="M194" t="inlineStr"/>
       <c r="N194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
       </c>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
       </c>
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
@@ -17049,7 +17049,7 @@
       </c>
       <c r="M198" t="inlineStr"/>
       <c r="N198" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
       </c>
       <c r="M199" t="inlineStr"/>
       <c r="N199" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="M200" t="inlineStr"/>
       <c r="N200" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
       </c>
       <c r="M202" t="inlineStr"/>
       <c r="N202" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
       </c>
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O203" t="inlineStr">
         <is>
@@ -17553,7 +17553,7 @@
       </c>
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
@@ -17637,7 +17637,7 @@
       </c>
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
@@ -17721,7 +17721,7 @@
       </c>
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="M207" t="inlineStr"/>
       <c r="N207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O207" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="M208" t="inlineStr"/>
       <c r="N208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
       </c>
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
       </c>
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
       </c>
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
       </c>
       <c r="M212" t="inlineStr"/>
       <c r="N212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
       </c>
       <c r="M213" t="inlineStr"/>
       <c r="N213" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -18393,7 +18393,7 @@
       </c>
       <c r="M214" t="inlineStr"/>
       <c r="N214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O214" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
       </c>
       <c r="M215" t="inlineStr"/>
       <c r="N215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O215" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
       </c>
       <c r="M216" t="inlineStr"/>
       <c r="N216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O216" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="M217" t="inlineStr"/>
       <c r="N217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="M218" t="inlineStr"/>
       <c r="N218" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O218" t="inlineStr">
         <is>
@@ -18813,7 +18813,7 @@
       </c>
       <c r="M219" t="inlineStr"/>
       <c r="N219" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
       </c>
       <c r="M220" t="inlineStr"/>
       <c r="N220" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
       </c>
       <c r="M221" t="inlineStr"/>
       <c r="N221" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O221" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
       </c>
       <c r="M222" t="inlineStr"/>
       <c r="N222" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
       </c>
       <c r="M223" t="inlineStr"/>
       <c r="N223" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
       </c>
       <c r="M224" t="inlineStr"/>
       <c r="N224" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O224" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
       </c>
       <c r="M225" t="inlineStr"/>
       <c r="N225" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
       </c>
       <c r="M226" t="inlineStr"/>
       <c r="N226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O226" t="inlineStr">
         <is>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="M227" t="inlineStr"/>
       <c r="N227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
       </c>
       <c r="M228" t="inlineStr"/>
       <c r="N228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="M229" t="inlineStr"/>
       <c r="N229" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
       </c>
       <c r="M230" t="inlineStr"/>
       <c r="N230" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="M231" t="inlineStr"/>
       <c r="N231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
       </c>
       <c r="M232" t="inlineStr"/>
       <c r="N232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O232" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
       </c>
       <c r="M233" t="inlineStr"/>
       <c r="N233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
       </c>
       <c r="M234" t="inlineStr"/>
       <c r="N234" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O234" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
       </c>
       <c r="M235" t="inlineStr"/>
       <c r="N235" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O235" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
       </c>
       <c r="M236" t="inlineStr"/>
       <c r="N236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O236" t="inlineStr">
         <is>
@@ -20325,7 +20325,7 @@
       </c>
       <c r="M237" t="inlineStr"/>
       <c r="N237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O237" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="M238" t="inlineStr"/>
       <c r="N238" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O238" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
       </c>
       <c r="M239" t="inlineStr"/>
       <c r="N239" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O239" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="M240" t="inlineStr"/>
       <c r="N240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
@@ -20661,7 +20661,7 @@
       </c>
       <c r="M241" t="inlineStr"/>
       <c r="N241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O241" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
       </c>
       <c r="M242" t="inlineStr"/>
       <c r="N242" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O242" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="M243" t="inlineStr"/>
       <c r="N243" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O243" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
       </c>
       <c r="M244" t="inlineStr"/>
       <c r="N244" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O244" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
       </c>
       <c r="M245" t="inlineStr"/>
       <c r="N245" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
@@ -21081,7 +21081,7 @@
       </c>
       <c r="M246" t="inlineStr"/>
       <c r="N246" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
       </c>
       <c r="M247" t="inlineStr"/>
       <c r="N247" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O247" t="inlineStr">
         <is>
@@ -21249,7 +21249,7 @@
       </c>
       <c r="M248" t="inlineStr"/>
       <c r="N248" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O248" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="M249" t="inlineStr"/>
       <c r="N249" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
@@ -21417,7 +21417,7 @@
       </c>
       <c r="M250" t="inlineStr"/>
       <c r="N250" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O250" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
       </c>
       <c r="M251" t="inlineStr"/>
       <c r="N251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O251" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
       </c>
       <c r="M252" t="inlineStr"/>
       <c r="N252" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O252" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
       </c>
       <c r="M253" t="inlineStr"/>
       <c r="N253" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O253" t="inlineStr">
         <is>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="M254" t="inlineStr"/>
       <c r="N254" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O254" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="M255" t="inlineStr"/>
       <c r="N255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
       </c>
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O256" t="inlineStr">
         <is>
@@ -22005,7 +22005,7 @@
       </c>
       <c r="M257" t="inlineStr"/>
       <c r="N257" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O257" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="M258" t="inlineStr"/>
       <c r="N258" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O258" t="inlineStr">
         <is>
@@ -22173,7 +22173,7 @@
       </c>
       <c r="M259" t="inlineStr"/>
       <c r="N259" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -22257,7 +22257,7 @@
       </c>
       <c r="M260" t="inlineStr"/>
       <c r="N260" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O260" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
       </c>
       <c r="M261" t="inlineStr"/>
       <c r="N261" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O261" t="inlineStr">
         <is>
@@ -22425,7 +22425,7 @@
       </c>
       <c r="M262" t="inlineStr"/>
       <c r="N262" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O262" t="inlineStr">
         <is>
@@ -22509,7 +22509,7 @@
       </c>
       <c r="M263" t="inlineStr"/>
       <c r="N263" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O263" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
       </c>
       <c r="M264" t="inlineStr"/>
       <c r="N264" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O264" t="inlineStr">
         <is>
@@ -22677,7 +22677,7 @@
       </c>
       <c r="M265" t="inlineStr"/>
       <c r="N265" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O265" t="inlineStr">
         <is>
@@ -22761,7 +22761,7 @@
       </c>
       <c r="M266" t="inlineStr"/>
       <c r="N266" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O266" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
       </c>
       <c r="M267" t="inlineStr"/>
       <c r="N267" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O267" t="inlineStr">
         <is>
@@ -22929,7 +22929,7 @@
       </c>
       <c r="M268" t="inlineStr"/>
       <c r="N268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O268" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
       </c>
       <c r="M269" t="inlineStr"/>
       <c r="N269" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O269" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
       </c>
       <c r="M270" t="inlineStr"/>
       <c r="N270" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O270" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
       </c>
       <c r="M271" t="inlineStr"/>
       <c r="N271" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O271" t="inlineStr">
         <is>
@@ -23265,7 +23265,7 @@
       </c>
       <c r="M272" t="inlineStr"/>
       <c r="N272" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O272" t="inlineStr">
         <is>
@@ -23349,7 +23349,7 @@
       </c>
       <c r="M273" t="inlineStr"/>
       <c r="N273" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O273" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="M274" t="inlineStr"/>
       <c r="N274" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O274" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
       </c>
       <c r="M275" t="inlineStr"/>
       <c r="N275" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O275" t="inlineStr">
         <is>
@@ -23601,7 +23601,7 @@
       </c>
       <c r="M276" t="inlineStr"/>
       <c r="N276" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O276" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
       </c>
       <c r="M277" t="inlineStr"/>
       <c r="N277" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O277" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
       </c>
       <c r="M278" t="inlineStr"/>
       <c r="N278" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O278" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="M279" t="inlineStr"/>
       <c r="N279" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O279" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="M280" t="inlineStr"/>
       <c r="N280" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
       </c>
       <c r="M281" t="inlineStr"/>
       <c r="N281" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O281" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
       </c>
       <c r="M282" t="inlineStr"/>
       <c r="N282" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O282" t="inlineStr">
         <is>
@@ -24189,7 +24189,7 @@
       </c>
       <c r="M283" t="inlineStr"/>
       <c r="N283" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O283" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
       </c>
       <c r="M284" t="inlineStr"/>
       <c r="N284" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O284" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
       </c>
       <c r="M285" t="inlineStr"/>
       <c r="N285" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O285" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
       </c>
       <c r="M286" t="inlineStr"/>
       <c r="N286" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O286" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
       </c>
       <c r="M287" t="inlineStr"/>
       <c r="N287" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O287" t="inlineStr">
         <is>
@@ -24609,7 +24609,7 @@
       </c>
       <c r="M288" t="inlineStr"/>
       <c r="N288" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O288" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="M289" t="inlineStr"/>
       <c r="N289" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O289" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
       </c>
       <c r="M290" t="inlineStr"/>
       <c r="N290" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O290" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
       </c>
       <c r="M291" t="inlineStr"/>
       <c r="N291" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O291" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
       </c>
       <c r="M292" t="inlineStr"/>
       <c r="N292" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O292" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
       </c>
       <c r="M293" t="inlineStr"/>
       <c r="N293" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O293" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
       </c>
       <c r="M294" t="inlineStr"/>
       <c r="N294" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O294" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
       </c>
       <c r="M295" t="inlineStr"/>
       <c r="N295" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O295" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
       </c>
       <c r="M296" t="inlineStr"/>
       <c r="N296" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O296" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
       </c>
       <c r="M297" t="inlineStr"/>
       <c r="N297" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O297" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
       </c>
       <c r="M298" t="inlineStr"/>
       <c r="N298" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O298" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
       </c>
       <c r="M299" t="inlineStr"/>
       <c r="N299" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
       </c>
       <c r="M300" t="inlineStr"/>
       <c r="N300" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O300" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
       </c>
       <c r="M301" t="inlineStr"/>
       <c r="N301" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O301" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
       </c>
       <c r="M302" t="inlineStr"/>
       <c r="N302" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O302" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
       </c>
       <c r="M303" t="inlineStr"/>
       <c r="N303" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O303" t="inlineStr">
         <is>
@@ -25953,7 +25953,7 @@
       </c>
       <c r="M304" t="inlineStr"/>
       <c r="N304" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O304" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
       </c>
       <c r="M305" t="inlineStr"/>
       <c r="N305" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O305" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="M306" t="inlineStr"/>
       <c r="N306" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O306" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
       </c>
       <c r="M307" t="inlineStr"/>
       <c r="N307" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O307" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
       </c>
       <c r="M308" t="inlineStr"/>
       <c r="N308" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O308" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
       </c>
       <c r="M309" t="inlineStr"/>
       <c r="N309" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O309" t="inlineStr">
         <is>
@@ -26457,7 +26457,7 @@
       </c>
       <c r="M310" t="inlineStr"/>
       <c r="N310" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O310" t="inlineStr">
         <is>
@@ -26541,7 +26541,7 @@
       </c>
       <c r="M311" t="inlineStr"/>
       <c r="N311" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O311" t="inlineStr">
         <is>
@@ -26625,7 +26625,7 @@
       </c>
       <c r="M312" t="inlineStr"/>
       <c r="N312" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O312" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
       </c>
       <c r="M313" t="inlineStr"/>
       <c r="N313" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O313" t="inlineStr">
         <is>
@@ -26793,7 +26793,7 @@
       </c>
       <c r="M314" t="inlineStr"/>
       <c r="N314" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O314" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
       </c>
       <c r="M315" t="inlineStr"/>
       <c r="N315" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O315" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
       </c>
       <c r="M316" t="inlineStr"/>
       <c r="N316" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O316" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
       </c>
       <c r="M317" t="inlineStr"/>
       <c r="N317" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O317" t="inlineStr">
         <is>
@@ -27129,7 +27129,7 @@
       </c>
       <c r="M318" t="inlineStr"/>
       <c r="N318" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O318" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
       </c>
       <c r="M319" t="inlineStr"/>
       <c r="N319" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
@@ -27297,7 +27297,7 @@
       </c>
       <c r="M320" t="inlineStr"/>
       <c r="N320" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O320" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
       </c>
       <c r="M321" t="inlineStr"/>
       <c r="N321" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O321" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
       </c>
       <c r="M322" t="inlineStr"/>
       <c r="N322" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O322" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="M323" t="inlineStr"/>
       <c r="N323" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O323" t="inlineStr">
         <is>
@@ -27633,7 +27633,7 @@
       </c>
       <c r="M324" t="inlineStr"/>
       <c r="N324" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O324" t="inlineStr">
         <is>
@@ -27717,7 +27717,7 @@
       </c>
       <c r="M325" t="inlineStr"/>
       <c r="N325" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O325" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
       </c>
       <c r="M326" t="inlineStr"/>
       <c r="N326" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O326" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
       </c>
       <c r="M327" t="inlineStr"/>
       <c r="N327" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O327" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
       </c>
       <c r="M328" t="inlineStr"/>
       <c r="N328" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O328" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
       </c>
       <c r="M329" t="inlineStr"/>
       <c r="N329" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O329" t="inlineStr">
         <is>
@@ -28137,7 +28137,7 @@
       </c>
       <c r="M330" t="inlineStr"/>
       <c r="N330" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O330" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
       </c>
       <c r="M331" t="inlineStr"/>
       <c r="N331" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O331" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
       </c>
       <c r="M332" t="inlineStr"/>
       <c r="N332" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O332" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
       </c>
       <c r="M333" t="inlineStr"/>
       <c r="N333" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O333" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
       </c>
       <c r="M334" t="inlineStr"/>
       <c r="N334" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O334" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
       </c>
       <c r="M335" t="inlineStr"/>
       <c r="N335" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O335" t="inlineStr">
         <is>
@@ -28641,7 +28641,7 @@
       </c>
       <c r="M336" t="inlineStr"/>
       <c r="N336" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O336" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
       </c>
       <c r="M337" t="inlineStr"/>
       <c r="N337" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O337" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
       </c>
       <c r="M338" t="inlineStr"/>
       <c r="N338" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O338" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
       </c>
       <c r="M339" t="inlineStr"/>
       <c r="N339" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O339" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
       </c>
       <c r="M340" t="inlineStr"/>
       <c r="N340" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O340" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
       </c>
       <c r="M341" t="inlineStr"/>
       <c r="N341" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O341" t="inlineStr">
         <is>
@@ -29145,7 +29145,7 @@
       </c>
       <c r="M342" t="inlineStr"/>
       <c r="N342" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O342" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
       </c>
       <c r="M343" t="inlineStr"/>
       <c r="N343" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O343" t="inlineStr">
         <is>
@@ -29313,7 +29313,7 @@
       </c>
       <c r="M344" t="inlineStr"/>
       <c r="N344" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O344" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
       </c>
       <c r="M345" t="inlineStr"/>
       <c r="N345" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O345" t="inlineStr">
         <is>
@@ -29481,7 +29481,7 @@
       </c>
       <c r="M346" t="inlineStr"/>
       <c r="N346" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O346" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
       </c>
       <c r="M347" t="inlineStr"/>
       <c r="N347" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O347" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
       </c>
       <c r="M348" t="inlineStr"/>
       <c r="N348" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O348" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
       </c>
       <c r="M349" t="inlineStr"/>
       <c r="N349" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O349" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
       </c>
       <c r="M350" t="inlineStr"/>
       <c r="N350" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O350" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
       </c>
       <c r="M351" t="inlineStr"/>
       <c r="N351" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O351" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
       </c>
       <c r="M352" t="inlineStr"/>
       <c r="N352" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O352" t="inlineStr">
         <is>
@@ -30069,7 +30069,7 @@
       </c>
       <c r="M353" t="inlineStr"/>
       <c r="N353" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O353" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
       </c>
       <c r="M354" t="inlineStr"/>
       <c r="N354" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O354" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
       </c>
       <c r="M355" t="inlineStr"/>
       <c r="N355" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O355" t="inlineStr">
         <is>
@@ -30321,7 +30321,7 @@
       </c>
       <c r="M356" t="inlineStr"/>
       <c r="N356" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O356" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
       </c>
       <c r="M357" t="inlineStr"/>
       <c r="N357" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O357" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
       </c>
       <c r="M358" t="inlineStr"/>
       <c r="N358" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O358" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
       </c>
       <c r="M359" t="inlineStr"/>
       <c r="N359" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O359" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
       </c>
       <c r="M360" t="inlineStr"/>
       <c r="N360" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O360" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
       </c>
       <c r="M361" t="inlineStr"/>
       <c r="N361" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O361" t="inlineStr">
         <is>
@@ -30825,7 +30825,7 @@
       </c>
       <c r="M362" t="inlineStr"/>
       <c r="N362" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O362" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
       </c>
       <c r="M363" t="inlineStr"/>
       <c r="N363" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O363" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
       </c>
       <c r="M364" t="inlineStr"/>
       <c r="N364" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O364" t="inlineStr">
         <is>
@@ -31077,7 +31077,7 @@
       </c>
       <c r="M365" t="inlineStr"/>
       <c r="N365" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O365" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
       </c>
       <c r="M366" t="inlineStr"/>
       <c r="N366" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O366" t="inlineStr">
         <is>
@@ -31245,7 +31245,7 @@
       </c>
       <c r="M367" t="inlineStr"/>
       <c r="N367" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O367" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
       </c>
       <c r="M368" t="inlineStr"/>
       <c r="N368" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O368" t="inlineStr">
         <is>
@@ -31413,7 +31413,7 @@
       </c>
       <c r="M369" t="inlineStr"/>
       <c r="N369" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O369" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
       </c>
       <c r="M370" t="inlineStr"/>
       <c r="N370" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O370" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
       </c>
       <c r="M371" t="inlineStr"/>
       <c r="N371" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O371" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
       </c>
       <c r="M372" t="inlineStr"/>
       <c r="N372" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O372" t="inlineStr">
         <is>
@@ -31749,7 +31749,7 @@
       </c>
       <c r="M373" t="inlineStr"/>
       <c r="N373" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O373" t="inlineStr">
         <is>
@@ -31833,7 +31833,7 @@
       </c>
       <c r="M374" t="inlineStr"/>
       <c r="N374" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O374" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
       </c>
       <c r="M375" t="inlineStr"/>
       <c r="N375" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O375" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="M376" t="inlineStr"/>
       <c r="N376" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O376" t="inlineStr">
         <is>
@@ -32085,7 +32085,7 @@
       </c>
       <c r="M377" t="inlineStr"/>
       <c r="N377" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O377" t="inlineStr">
         <is>
@@ -32169,7 +32169,7 @@
       </c>
       <c r="M378" t="inlineStr"/>
       <c r="N378" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O378" t="inlineStr">
         <is>
@@ -32253,7 +32253,7 @@
       </c>
       <c r="M379" t="inlineStr"/>
       <c r="N379" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O379" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
       </c>
       <c r="M380" t="inlineStr"/>
       <c r="N380" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O380" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
       </c>
       <c r="M381" t="inlineStr"/>
       <c r="N381" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O381" t="inlineStr">
         <is>
@@ -32505,7 +32505,7 @@
       </c>
       <c r="M382" t="inlineStr"/>
       <c r="N382" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O382" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
       </c>
       <c r="M383" t="inlineStr"/>
       <c r="N383" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O383" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
       </c>
       <c r="M384" t="inlineStr"/>
       <c r="N384" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O384" t="inlineStr">
         <is>
@@ -32757,7 +32757,7 @@
       </c>
       <c r="M385" t="inlineStr"/>
       <c r="N385" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O385" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
       </c>
       <c r="M386" t="inlineStr"/>
       <c r="N386" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O386" t="inlineStr">
         <is>
@@ -32925,7 +32925,7 @@
       </c>
       <c r="M387" t="inlineStr"/>
       <c r="N387" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O387" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
       </c>
       <c r="M388" t="inlineStr"/>
       <c r="N388" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O388" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
       </c>
       <c r="M389" t="inlineStr"/>
       <c r="N389" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O389" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
       </c>
       <c r="M390" t="inlineStr"/>
       <c r="N390" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O390" t="inlineStr">
         <is>
@@ -33261,7 +33261,7 @@
       </c>
       <c r="M391" t="inlineStr"/>
       <c r="N391" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O391" t="inlineStr">
         <is>
@@ -33345,7 +33345,7 @@
       </c>
       <c r="M392" t="inlineStr"/>
       <c r="N392" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O392" t="inlineStr">
         <is>
@@ -33429,7 +33429,7 @@
       </c>
       <c r="M393" t="inlineStr"/>
       <c r="N393" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O393" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
       </c>
       <c r="M394" t="inlineStr"/>
       <c r="N394" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O394" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
       </c>
       <c r="M395" t="inlineStr"/>
       <c r="N395" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O395" t="inlineStr">
         <is>
@@ -33681,7 +33681,7 @@
       </c>
       <c r="M396" t="inlineStr"/>
       <c r="N396" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O396" t="inlineStr">
         <is>
@@ -33765,7 +33765,7 @@
       </c>
       <c r="M397" t="inlineStr"/>
       <c r="N397" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O397" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="M398" t="inlineStr"/>
       <c r="N398" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O398" t="inlineStr">
         <is>
@@ -33933,7 +33933,7 @@
       </c>
       <c r="M399" t="inlineStr"/>
       <c r="N399" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O399" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
       </c>
       <c r="M400" t="inlineStr"/>
       <c r="N400" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O400" t="inlineStr">
         <is>
@@ -34101,7 +34101,7 @@
       </c>
       <c r="M401" t="inlineStr"/>
       <c r="N401" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O401" t="inlineStr">
         <is>
@@ -34185,7 +34185,7 @@
       </c>
       <c r="M402" t="inlineStr"/>
       <c r="N402" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O402" t="inlineStr">
         <is>
@@ -34269,7 +34269,7 @@
       </c>
       <c r="M403" t="inlineStr"/>
       <c r="N403" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O403" t="inlineStr">
         <is>
@@ -34353,7 +34353,7 @@
       </c>
       <c r="M404" t="inlineStr"/>
       <c r="N404" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O404" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
       </c>
       <c r="M405" t="inlineStr"/>
       <c r="N405" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O405" t="inlineStr">
         <is>
@@ -34521,7 +34521,7 @@
       </c>
       <c r="M406" t="inlineStr"/>
       <c r="N406" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O406" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
       </c>
       <c r="M407" t="inlineStr"/>
       <c r="N407" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O407" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
       </c>
       <c r="M408" t="inlineStr"/>
       <c r="N408" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O408" t="inlineStr">
         <is>
@@ -34773,7 +34773,7 @@
       </c>
       <c r="M409" t="inlineStr"/>
       <c r="N409" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O409" t="inlineStr">
         <is>
@@ -34857,7 +34857,7 @@
       </c>
       <c r="M410" t="inlineStr"/>
       <c r="N410" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O410" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
       </c>
       <c r="M411" t="inlineStr"/>
       <c r="N411" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O411" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
       </c>
       <c r="M412" t="inlineStr"/>
       <c r="N412" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O412" t="inlineStr">
         <is>
@@ -35109,7 +35109,7 @@
       </c>
       <c r="M413" t="inlineStr"/>
       <c r="N413" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O413" t="inlineStr">
         <is>
@@ -35193,7 +35193,7 @@
       </c>
       <c r="M414" t="inlineStr"/>
       <c r="N414" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O414" t="inlineStr">
         <is>
@@ -35277,7 +35277,7 @@
       </c>
       <c r="M415" t="inlineStr"/>
       <c r="N415" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O415" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
       </c>
       <c r="M416" t="inlineStr"/>
       <c r="N416" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O416" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
       </c>
       <c r="M417" t="inlineStr"/>
       <c r="N417" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O417" t="inlineStr">
         <is>
@@ -35529,7 +35529,7 @@
       </c>
       <c r="M418" t="inlineStr"/>
       <c r="N418" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O418" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
       </c>
       <c r="M419" t="inlineStr"/>
       <c r="N419" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O419" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
       </c>
       <c r="M420" t="inlineStr"/>
       <c r="N420" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O420" t="inlineStr">
         <is>
@@ -35781,7 +35781,7 @@
       </c>
       <c r="M421" t="inlineStr"/>
       <c r="N421" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O421" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
       </c>
       <c r="M422" t="inlineStr"/>
       <c r="N422" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O422" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
       </c>
       <c r="M423" t="inlineStr"/>
       <c r="N423" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O423" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
       </c>
       <c r="M424" t="inlineStr"/>
       <c r="N424" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O424" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
       </c>
       <c r="M425" t="inlineStr"/>
       <c r="N425" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O425" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
       </c>
       <c r="M426" t="inlineStr"/>
       <c r="N426" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O426" t="inlineStr">
         <is>
@@ -36285,7 +36285,7 @@
       </c>
       <c r="M427" t="inlineStr"/>
       <c r="N427" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O427" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
       </c>
       <c r="M428" t="inlineStr"/>
       <c r="N428" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O428" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
       </c>
       <c r="M429" t="inlineStr"/>
       <c r="N429" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O429" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
       </c>
       <c r="M430" t="inlineStr"/>
       <c r="N430" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O430" t="inlineStr">
         <is>
@@ -36621,7 +36621,7 @@
       </c>
       <c r="M431" t="inlineStr"/>
       <c r="N431" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O431" t="inlineStr">
         <is>
@@ -36709,7 +36709,7 @@
         </is>
       </c>
       <c r="N432" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O432" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
       </c>
       <c r="R432" t="inlineStr">
         <is>
-          <t>2026-05-11T20:31:48.747700+00:00</t>
+          <t>2026-05-11T22:05:54.077541+00:00</t>
         </is>
       </c>
     </row>
@@ -36793,7 +36793,7 @@
         </is>
       </c>
       <c r="N433" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O433" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
       </c>
       <c r="R433" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:36.364286+00:00</t>
+          <t>2026-05-11T22:05:54.077541+00:00</t>
         </is>
       </c>
     </row>
@@ -36877,7 +36877,7 @@
         </is>
       </c>
       <c r="N434" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O434" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
       </c>
       <c r="R434" t="inlineStr">
         <is>
-          <t>2026-05-11T20:31:50.503843+00:00</t>
+          <t>2026-05-11T22:05:54.077541+00:00</t>
         </is>
       </c>
     </row>
@@ -36961,7 +36961,7 @@
         </is>
       </c>
       <c r="N435" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O435" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
       </c>
       <c r="R435" t="inlineStr">
         <is>
-          <t>2026-05-11T20:33:00.077795+00:00</t>
+          <t>2026-05-11T22:05:54.077541+00:00</t>
         </is>
       </c>
     </row>
@@ -37060,7 +37060,7 @@
       </c>
       <c r="R436" t="inlineStr">
         <is>
-          <t>2026-05-11T20:31:52.767981+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -37144,7 +37144,7 @@
       </c>
       <c r="R437" t="inlineStr">
         <is>
-          <t>2026-05-11T20:33:02.337378+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -37228,7 +37228,7 @@
       </c>
       <c r="R438" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:38.649869+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -37312,7 +37312,7 @@
       </c>
       <c r="R439" t="inlineStr">
         <is>
-          <t>2026-05-11T20:31:55.099713+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -37396,7 +37396,7 @@
       </c>
       <c r="R440" t="inlineStr">
         <is>
-          <t>2026-05-11T20:31:57.533996+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -37480,7 +37480,7 @@
       </c>
       <c r="R441" t="inlineStr">
         <is>
-          <t>2026-05-11T20:33:04.760520+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -37564,7 +37564,7 @@
       </c>
       <c r="R442" t="inlineStr">
         <is>
-          <t>2026-05-11T20:31:59.904051+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -37648,7 +37648,7 @@
       </c>
       <c r="R443" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:41.043509+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="R444" t="inlineStr">
         <is>
-          <t>2026-05-11T20:33:07.157955+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -37816,7 +37816,7 @@
       </c>
       <c r="R445" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:02.313975+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -37900,7 +37900,7 @@
       </c>
       <c r="R446" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:05.039112+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -37984,7 +37984,7 @@
       </c>
       <c r="R447" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:07.333431+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -38068,7 +38068,7 @@
       </c>
       <c r="R448" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:09.572980+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -38152,7 +38152,7 @@
       </c>
       <c r="R449" t="inlineStr">
         <is>
-          <t>2026-05-11T20:33:10.035549+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -38236,7 +38236,7 @@
       </c>
       <c r="R450" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:11.912767+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -38320,7 +38320,7 @@
       </c>
       <c r="R451" t="inlineStr">
         <is>
-          <t>2026-05-11T20:33:11.954217+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -38404,7 +38404,7 @@
       </c>
       <c r="R452" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:14.300502+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -38488,7 +38488,7 @@
       </c>
       <c r="R453" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:17.053840+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -38572,7 +38572,7 @@
       </c>
       <c r="R454" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:43.378048+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -38656,7 +38656,7 @@
       </c>
       <c r="R455" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:45.642221+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -38740,7 +38740,7 @@
       </c>
       <c r="R456" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:19.310764+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -38824,7 +38824,7 @@
       </c>
       <c r="R457" t="inlineStr">
         <is>
-          <t>2026-05-11T20:33:14.347784+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -38908,7 +38908,7 @@
       </c>
       <c r="R458" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:21.695246+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -38992,7 +38992,7 @@
       </c>
       <c r="R459" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:23.931853+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -39076,7 +39076,7 @@
       </c>
       <c r="R460" t="inlineStr">
         <is>
-          <t>2026-05-11T20:33:16.729071+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -39160,7 +39160,7 @@
       </c>
       <c r="R461" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:47.947838+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -39244,7 +39244,7 @@
       </c>
       <c r="R462" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:26.694113+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -39328,7 +39328,7 @@
       </c>
       <c r="R463" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:28.937089+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -39412,7 +39412,7 @@
       </c>
       <c r="R464" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:50.326816+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -39496,7 +39496,7 @@
       </c>
       <c r="R465" t="inlineStr">
         <is>
-          <t>2026-05-11T20:33:19.520351+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -39580,7 +39580,7 @@
       </c>
       <c r="R466" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:52.743564+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -39664,7 +39664,7 @@
       </c>
       <c r="R467" t="inlineStr">
         <is>
-          <t>2026-05-11T20:33:21.787082+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -39748,7 +39748,7 @@
       </c>
       <c r="R468" t="inlineStr">
         <is>
-          <t>2026-05-11T20:33:24.008183+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -39832,7 +39832,7 @@
       </c>
       <c r="R469" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:31.171390+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -39916,7 +39916,7 @@
       </c>
       <c r="R470" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:33.517559+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -40000,7 +40000,7 @@
       </c>
       <c r="R471" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:55.487723+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -40084,7 +40084,7 @@
       </c>
       <c r="R472" t="inlineStr">
         <is>
-          <t>2026-05-11T20:33:26.359452+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -40168,7 +40168,7 @@
       </c>
       <c r="R473" t="inlineStr">
         <is>
-          <t>2026-05-11T20:33:29.093063+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>
@@ -40252,7 +40252,7 @@
       </c>
       <c r="R474" t="inlineStr">
         <is>
-          <t>2026-05-11T20:32:57.824496+00:00</t>
+          <t>2026-05-12T06:51:32.828510+00:00</t>
         </is>
       </c>
     </row>

--- a/data/tournaments_master.xlsx
+++ b/data/tournaments_master.xlsx
@@ -37021,7 +37021,7 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>Подача поздних заявок</t>
+          <t>Все</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -37060,7 +37060,7 @@
       </c>
       <c r="R436" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -37144,7 +37144,7 @@
       </c>
       <c r="R437" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -37228,7 +37228,7 @@
       </c>
       <c r="R438" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -37312,7 +37312,7 @@
       </c>
       <c r="R439" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -37396,7 +37396,7 @@
       </c>
       <c r="R440" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -37441,7 +37441,7 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -37480,7 +37480,7 @@
       </c>
       <c r="R441" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -37564,7 +37564,7 @@
       </c>
       <c r="R442" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -37648,7 +37648,7 @@
       </c>
       <c r="R443" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="R444" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -37816,7 +37816,7 @@
       </c>
       <c r="R445" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -37900,7 +37900,7 @@
       </c>
       <c r="R446" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -37984,7 +37984,7 @@
       </c>
       <c r="R447" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -38068,7 +38068,7 @@
       </c>
       <c r="R448" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -38152,7 +38152,7 @@
       </c>
       <c r="R449" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -38236,7 +38236,7 @@
       </c>
       <c r="R450" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -38320,7 +38320,7 @@
       </c>
       <c r="R451" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -38404,7 +38404,7 @@
       </c>
       <c r="R452" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -38488,7 +38488,7 @@
       </c>
       <c r="R453" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -38572,7 +38572,7 @@
       </c>
       <c r="R454" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -38656,7 +38656,7 @@
       </c>
       <c r="R455" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -38740,7 +38740,7 @@
       </c>
       <c r="R456" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -38824,7 +38824,7 @@
       </c>
       <c r="R457" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -38908,7 +38908,7 @@
       </c>
       <c r="R458" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -38992,7 +38992,7 @@
       </c>
       <c r="R459" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -39076,7 +39076,7 @@
       </c>
       <c r="R460" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -39160,7 +39160,7 @@
       </c>
       <c r="R461" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -39244,7 +39244,7 @@
       </c>
       <c r="R462" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -39328,7 +39328,7 @@
       </c>
       <c r="R463" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -39412,7 +39412,7 @@
       </c>
       <c r="R464" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -39496,7 +39496,7 @@
       </c>
       <c r="R465" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -39580,7 +39580,7 @@
       </c>
       <c r="R466" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -39664,7 +39664,7 @@
       </c>
       <c r="R467" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -39748,7 +39748,7 @@
       </c>
       <c r="R468" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -39832,7 +39832,7 @@
       </c>
       <c r="R469" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -39916,7 +39916,7 @@
       </c>
       <c r="R470" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -40000,7 +40000,7 @@
       </c>
       <c r="R471" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -40084,7 +40084,7 @@
       </c>
       <c r="R472" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -40168,7 +40168,7 @@
       </c>
       <c r="R473" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>
@@ -40252,7 +40252,7 @@
       </c>
       <c r="R474" t="inlineStr">
         <is>
-          <t>2026-05-12T06:51:32.828510+00:00</t>
+          <t>2026-05-14T11:23:51.011172+00:00</t>
         </is>
       </c>
     </row>

--- a/data/tournaments_master.xlsx
+++ b/data/tournaments_master.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R474"/>
+  <dimension ref="A1:R502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37021,7 +37021,7 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>Все</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -37045,7 +37045,7 @@
         </is>
       </c>
       <c r="N436" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O436" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
       </c>
       <c r="R436" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-05-17T18:55:42.622398+00:00</t>
         </is>
       </c>
     </row>
@@ -37105,7 +37105,7 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>Подача поздних заявок</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -37129,7 +37129,7 @@
         </is>
       </c>
       <c r="N437" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O437" t="inlineStr">
         <is>
@@ -37144,7 +37144,7 @@
       </c>
       <c r="R437" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-05-17T18:55:42.622398+00:00</t>
         </is>
       </c>
     </row>
@@ -37189,7 +37189,7 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Подача поздних заявок</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -37213,7 +37213,7 @@
         </is>
       </c>
       <c r="N438" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O438" t="inlineStr">
         <is>
@@ -37228,7 +37228,7 @@
       </c>
       <c r="R438" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-05-17T18:55:42.622398+00:00</t>
         </is>
       </c>
     </row>
@@ -37273,7 +37273,7 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>Подача поздних заявок</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -37297,7 +37297,7 @@
         </is>
       </c>
       <c r="N439" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O439" t="inlineStr">
         <is>
@@ -37312,7 +37312,7 @@
       </c>
       <c r="R439" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-05-17T18:55:42.622398+00:00</t>
         </is>
       </c>
     </row>
@@ -37381,7 +37381,7 @@
         </is>
       </c>
       <c r="N440" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O440" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
       </c>
       <c r="R440" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-05-17T18:55:42.622398+00:00</t>
         </is>
       </c>
     </row>
@@ -37465,7 +37465,7 @@
         </is>
       </c>
       <c r="N441" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O441" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
       </c>
       <c r="R441" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-05-17T18:55:42.622398+00:00</t>
         </is>
       </c>
     </row>
@@ -37549,7 +37549,7 @@
         </is>
       </c>
       <c r="N442" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O442" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
       </c>
       <c r="R442" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-05-17T18:55:42.622398+00:00</t>
         </is>
       </c>
     </row>
@@ -37633,7 +37633,7 @@
         </is>
       </c>
       <c r="N443" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O443" t="inlineStr">
         <is>
@@ -37648,7 +37648,7 @@
       </c>
       <c r="R443" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-05-17T18:55:42.622398+00:00</t>
         </is>
       </c>
     </row>
@@ -37717,7 +37717,7 @@
         </is>
       </c>
       <c r="N444" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O444" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
       </c>
       <c r="R444" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-05-17T18:55:42.622398+00:00</t>
         </is>
       </c>
     </row>
@@ -37801,7 +37801,7 @@
         </is>
       </c>
       <c r="N445" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O445" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
       </c>
       <c r="R445" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-05-17T18:55:42.622398+00:00</t>
         </is>
       </c>
     </row>
@@ -37861,17 +37861,17 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>Подача поздних заявок</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>V А</t>
+          <t>Все</t>
         </is>
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>Олимпийская</t>
+          <t>Все</t>
         </is>
       </c>
       <c r="L446" t="inlineStr">
@@ -37885,14 +37885,18 @@
         </is>
       </c>
       <c r="N446" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O446" t="inlineStr">
         <is>
-          <t>rtt_calendar</t>
-        </is>
-      </c>
-      <c r="P446" t="inlineStr"/>
+          <t>legacy_excel</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q446" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:12.363735+00:00</t>
@@ -37900,7 +37904,7 @@
       </c>
       <c r="R446" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-01T14:55:30.287435+00:00</t>
         </is>
       </c>
     </row>
@@ -37945,7 +37949,7 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
@@ -37969,14 +37973,18 @@
         </is>
       </c>
       <c r="N447" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O447" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P447" t="inlineStr"/>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q447" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:12.363735+00:00</t>
@@ -37984,7 +37992,7 @@
       </c>
       <c r="R447" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-01T14:58:31.336903+00:00</t>
         </is>
       </c>
     </row>
@@ -38029,7 +38037,7 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -38053,14 +38061,18 @@
         </is>
       </c>
       <c r="N448" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O448" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P448" t="inlineStr"/>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q448" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:12.363735+00:00</t>
@@ -38068,7 +38080,7 @@
       </c>
       <c r="R448" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-01T14:58:31.336903+00:00</t>
         </is>
       </c>
     </row>
@@ -38113,7 +38125,7 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Все</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
@@ -38137,14 +38149,18 @@
         </is>
       </c>
       <c r="N449" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O449" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P449" t="inlineStr"/>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q449" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:44.681774+00:00</t>
@@ -38152,7 +38168,7 @@
       </c>
       <c r="R449" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-01T14:58:31.336903+00:00</t>
         </is>
       </c>
     </row>
@@ -38197,7 +38213,7 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
@@ -38221,14 +38237,18 @@
         </is>
       </c>
       <c r="N450" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O450" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P450" t="inlineStr"/>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q450" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:12.363735+00:00</t>
@@ -38236,7 +38256,7 @@
       </c>
       <c r="R450" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-01T14:58:31.336903+00:00</t>
         </is>
       </c>
     </row>
@@ -38281,7 +38301,7 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
@@ -38305,14 +38325,18 @@
         </is>
       </c>
       <c r="N451" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O451" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P451" t="inlineStr"/>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q451" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:44.681774+00:00</t>
@@ -38320,7 +38344,7 @@
       </c>
       <c r="R451" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-01T14:58:31.336903+00:00</t>
         </is>
       </c>
     </row>
@@ -38365,7 +38389,7 @@
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
@@ -38389,14 +38413,18 @@
         </is>
       </c>
       <c r="N452" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O452" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P452" t="inlineStr"/>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q452" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:12.363735+00:00</t>
@@ -38404,7 +38432,7 @@
       </c>
       <c r="R452" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-08T06:20:27.286668+00:00</t>
         </is>
       </c>
     </row>
@@ -38449,7 +38477,7 @@
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -38473,14 +38501,18 @@
         </is>
       </c>
       <c r="N453" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O453" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P453" t="inlineStr"/>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q453" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:12.363735+00:00</t>
@@ -38488,7 +38520,7 @@
       </c>
       <c r="R453" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-08T06:20:27.286668+00:00</t>
         </is>
       </c>
     </row>
@@ -38533,7 +38565,7 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
@@ -38557,14 +38589,18 @@
         </is>
       </c>
       <c r="N454" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O454" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P454" t="inlineStr"/>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q454" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:28.549184+00:00</t>
@@ -38572,7 +38608,7 @@
       </c>
       <c r="R454" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-08T06:20:27.286668+00:00</t>
         </is>
       </c>
     </row>
@@ -38617,7 +38653,7 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -38641,14 +38677,18 @@
         </is>
       </c>
       <c r="N455" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O455" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P455" t="inlineStr"/>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q455" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:28.549184+00:00</t>
@@ -38656,7 +38696,7 @@
       </c>
       <c r="R455" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-08T06:20:27.286668+00:00</t>
         </is>
       </c>
     </row>
@@ -38701,7 +38741,7 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
@@ -38725,14 +38765,18 @@
         </is>
       </c>
       <c r="N456" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O456" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P456" t="inlineStr"/>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q456" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:12.363735+00:00</t>
@@ -38740,7 +38784,7 @@
       </c>
       <c r="R456" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-08T06:20:27.286668+00:00</t>
         </is>
       </c>
     </row>
@@ -38785,7 +38829,7 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
@@ -38809,14 +38853,18 @@
         </is>
       </c>
       <c r="N457" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O457" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P457" t="inlineStr"/>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q457" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:44.681774+00:00</t>
@@ -38824,7 +38872,7 @@
       </c>
       <c r="R457" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-08T06:20:27.286668+00:00</t>
         </is>
       </c>
     </row>
@@ -38869,7 +38917,7 @@
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
@@ -38893,14 +38941,18 @@
         </is>
       </c>
       <c r="N458" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O458" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P458" t="inlineStr"/>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q458" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:12.363735+00:00</t>
@@ -38908,7 +38960,7 @@
       </c>
       <c r="R458" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-08T06:20:27.286668+00:00</t>
         </is>
       </c>
     </row>
@@ -38953,7 +39005,7 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
@@ -38977,14 +39029,18 @@
         </is>
       </c>
       <c r="N459" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O459" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P459" t="inlineStr"/>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q459" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:12.363735+00:00</t>
@@ -38992,7 +39048,7 @@
       </c>
       <c r="R459" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-08T06:20:27.286668+00:00</t>
         </is>
       </c>
     </row>
@@ -39037,7 +39093,7 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -39061,14 +39117,18 @@
         </is>
       </c>
       <c r="N460" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O460" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P460" t="inlineStr"/>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q460" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:44.681774+00:00</t>
@@ -39076,7 +39136,7 @@
       </c>
       <c r="R460" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-08T06:20:27.286668+00:00</t>
         </is>
       </c>
     </row>
@@ -39121,7 +39181,7 @@
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
@@ -39145,14 +39205,18 @@
         </is>
       </c>
       <c r="N461" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O461" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P461" t="inlineStr"/>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q461" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:28.549184+00:00</t>
@@ -39160,7 +39224,7 @@
       </c>
       <c r="R461" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-08T06:20:27.286668+00:00</t>
         </is>
       </c>
     </row>
@@ -39205,7 +39269,7 @@
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
@@ -39229,14 +39293,18 @@
         </is>
       </c>
       <c r="N462" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O462" t="inlineStr">
         <is>
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P462" t="inlineStr"/>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q462" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:12.363735+00:00</t>
@@ -39244,7 +39312,7 @@
       </c>
       <c r="R462" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-08T06:20:27.286668+00:00</t>
         </is>
       </c>
     </row>
@@ -39289,7 +39357,7 @@
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
@@ -39320,7 +39388,11 @@
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P463" t="inlineStr"/>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q463" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:12.363735+00:00</t>
@@ -39328,7 +39400,7 @@
       </c>
       <c r="R463" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
         </is>
       </c>
     </row>
@@ -39373,7 +39445,7 @@
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>В процессе проведения</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -39404,7 +39476,11 @@
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P464" t="inlineStr"/>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q464" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:28.549184+00:00</t>
@@ -39412,7 +39488,7 @@
       </c>
       <c r="R464" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
         </is>
       </c>
     </row>
@@ -39457,7 +39533,7 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
@@ -39488,7 +39564,11 @@
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P465" t="inlineStr"/>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q465" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:44.681774+00:00</t>
@@ -39496,7 +39576,7 @@
       </c>
       <c r="R465" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
         </is>
       </c>
     </row>
@@ -39541,7 +39621,7 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
@@ -39572,7 +39652,11 @@
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P466" t="inlineStr"/>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q466" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:28.549184+00:00</t>
@@ -39580,7 +39664,7 @@
       </c>
       <c r="R466" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
         </is>
       </c>
     </row>
@@ -39625,7 +39709,7 @@
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -39656,7 +39740,11 @@
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P467" t="inlineStr"/>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q467" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:44.681774+00:00</t>
@@ -39664,7 +39752,7 @@
       </c>
       <c r="R467" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
         </is>
       </c>
     </row>
@@ -39709,7 +39797,7 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
@@ -39740,7 +39828,11 @@
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P468" t="inlineStr"/>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q468" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:44.681774+00:00</t>
@@ -39748,24 +39840,24 @@
       </c>
       <c r="R468" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>305454</t>
+          <t>305659</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Первенство Рязанской области</t>
+          <t>Чемпионат и Первенство Сергиево-Посадского городского округа "Золотые Купола"</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>до 17 лет</t>
+          <t>Взрослые</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -39785,20 +39877,20 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>Рязань</t>
+          <t>Сергиев Посад</t>
         </is>
       </c>
       <c r="H469" s="2" t="n">
-        <v>46202</v>
+        <v>46195</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>III А</t>
+          <t>IV А</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
@@ -39808,12 +39900,12 @@
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>https://rtt.mytennis.online/public/tours/305454/matches</t>
+          <t>https://rtt.mytennis.online/public/tours/305659/matches</t>
         </is>
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>https://rtt.mytennis.online/public/tours/305454/dashboard</t>
+          <t>https://rtt.mytennis.online/public/tours/305659/dashboard</t>
         </is>
       </c>
       <c r="N469" t="b">
@@ -39824,27 +39916,31 @@
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P469" t="inlineStr"/>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q469" t="inlineStr">
         <is>
-          <t>2026-05-11T20:31:12.363735+00:00</t>
+          <t>2026-05-29T06:02:24.670683+00:00</t>
         </is>
       </c>
       <c r="R469" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>305217</t>
+          <t>305454</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Турнир Кубок "Мостеннис"</t>
+          <t>Первенство Рязанской области</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -39869,20 +39965,20 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Воскресенск</t>
+          <t>Рязань</t>
         </is>
       </c>
       <c r="H470" s="2" t="n">
-        <v>46207</v>
+        <v>46202</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>V А</t>
+          <t>III А</t>
         </is>
       </c>
       <c r="K470" t="inlineStr">
@@ -39892,12 +39988,12 @@
       </c>
       <c r="L470" t="inlineStr">
         <is>
-          <t>https://rtt.mytennis.online/public/tours/305217/matches</t>
+          <t>https://rtt.mytennis.online/public/tours/305454/matches</t>
         </is>
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>https://rtt.mytennis.online/public/tours/305217/dashboard</t>
+          <t>https://rtt.mytennis.online/public/tours/305454/dashboard</t>
         </is>
       </c>
       <c r="N470" t="b">
@@ -39908,7 +40004,11 @@
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P470" t="inlineStr"/>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q470" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:12.363735+00:00</t>
@@ -39916,24 +40016,24 @@
       </c>
       <c r="R470" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>305559</t>
+          <t>305692</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Кубок Федерации тенниса Воронежской области</t>
+          <t>Турнир "Кубок Жемчужины Подмосковья"</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>до 19 лет</t>
+          <t>до 17 лет</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -39953,20 +40053,20 @@
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>Воронеж</t>
+          <t>Истра</t>
         </is>
       </c>
       <c r="H471" s="2" t="n">
-        <v>46209</v>
+        <v>46202</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>III Б</t>
+          <t>IV Б</t>
         </is>
       </c>
       <c r="K471" t="inlineStr">
@@ -39976,12 +40076,12 @@
       </c>
       <c r="L471" t="inlineStr">
         <is>
-          <t>https://rtt.mytennis.online/public/tours/305559/matches</t>
+          <t>https://rtt.mytennis.online/public/tours/305692/matches</t>
         </is>
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>https://rtt.mytennis.online/public/tours/305559/dashboard</t>
+          <t>https://rtt.mytennis.online/public/tours/305692/dashboard</t>
         </is>
       </c>
       <c r="N471" t="b">
@@ -39992,32 +40092,36 @@
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P471" t="inlineStr"/>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q471" t="inlineStr">
         <is>
-          <t>2026-05-11T20:31:28.549184+00:00</t>
+          <t>2026-05-29T06:01:50.436836+00:00</t>
         </is>
       </c>
       <c r="R471" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>305505</t>
+          <t>305757</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Турнир города Москвы А Л Т - ИЮЛЬ (Включен в ЕКП Москомспорта)</t>
+          <t>Первенство Одинцовского городского округа Московской области "Гранд Теннис"</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Взрослые</t>
+          <t>до 17 лет</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -40037,20 +40141,20 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Одинцово</t>
         </is>
       </c>
       <c r="H472" s="2" t="n">
-        <v>46216</v>
+        <v>46202</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>V Б</t>
+          <t>IV А</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
@@ -40060,12 +40164,12 @@
       </c>
       <c r="L472" t="inlineStr">
         <is>
-          <t>https://rtt.mytennis.online/public/tours/305505/matches</t>
+          <t>https://rtt.mytennis.online/public/tours/305757/matches</t>
         </is>
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>https://rtt.mytennis.online/public/tours/305505/dashboard</t>
+          <t>https://rtt.mytennis.online/public/tours/305757/dashboard</t>
         </is>
       </c>
       <c r="N472" t="b">
@@ -40076,27 +40180,31 @@
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P472" t="inlineStr"/>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q472" t="inlineStr">
         <is>
-          <t>2026-05-11T20:31:44.681774+00:00</t>
+          <t>2026-05-29T06:01:50.436836+00:00</t>
         </is>
       </c>
       <c r="R472" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>305578</t>
+          <t>305769</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Всероссийские соревнования</t>
+          <t>Чемпионат Одинцовского городского округа Московской области "Гранд Теннис"</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -40121,20 +40229,20 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>Одинцово</t>
         </is>
       </c>
       <c r="H473" s="2" t="n">
-        <v>46223</v>
+        <v>46202</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>Подача заявок</t>
+          <t>Подача поздних заявок</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>I А</t>
+          <t>IV А</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
@@ -40144,12 +40252,12 @@
       </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>https://rtt.mytennis.online/public/tours/305578/matches</t>
+          <t>https://rtt.mytennis.online/public/tours/305769/matches</t>
         </is>
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>https://rtt.mytennis.online/public/tours/305578/dashboard</t>
+          <t>https://rtt.mytennis.online/public/tours/305769/dashboard</t>
         </is>
       </c>
       <c r="N473" t="b">
@@ -40160,27 +40268,31 @@
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P473" t="inlineStr"/>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q473" t="inlineStr">
         <is>
-          <t>2026-05-11T20:31:44.681774+00:00</t>
+          <t>2026-05-29T06:02:24.670683+00:00</t>
         </is>
       </c>
       <c r="R473" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>305529</t>
+          <t>305559</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Первенство Тверской области</t>
+          <t>Кубок Федерации тенниса Воронежской области</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -40205,11 +40317,11 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>Вышний Волочек</t>
+          <t>Воронеж</t>
         </is>
       </c>
       <c r="H474" s="2" t="n">
-        <v>46230</v>
+        <v>46209</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -40218,22 +40330,22 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>III А</t>
+          <t>III Б</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>Олимпийская</t>
+          <t>Олимпийская и ДТ</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
         <is>
-          <t>https://rtt.mytennis.online/public/tours/305529/matches</t>
+          <t>https://rtt.mytennis.online/public/tours/305559/matches</t>
         </is>
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>https://rtt.mytennis.online/public/tours/305529/dashboard</t>
+          <t>https://rtt.mytennis.online/public/tours/305559/dashboard</t>
         </is>
       </c>
       <c r="N474" t="b">
@@ -40244,7 +40356,11 @@
           <t>rtt_calendar</t>
         </is>
       </c>
-      <c r="P474" t="inlineStr"/>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
       <c r="Q474" t="inlineStr">
         <is>
           <t>2026-05-11T20:31:28.549184+00:00</t>
@@ -40252,7 +40368,2415 @@
       </c>
       <c r="R474" t="inlineStr">
         <is>
-          <t>2026-05-14T11:23:51.011172+00:00</t>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>305907</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Чемпионат и Первенство Сергиево-Посадского городского округа "Золотые Купола"</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Взрослые</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Сергиев Посад</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>IV А</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305907/matches</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305907/dashboard</t>
+        </is>
+      </c>
+      <c r="N475" t="b">
+        <v>0</v>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr"/>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:56:41.903320+00:00</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>305908</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Чемпионат и Первенство Сергиево-Посадского городского округа "Золотые Купола"</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Сергиев Посад</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>IV А</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305908/matches</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305908/dashboard</t>
+        </is>
+      </c>
+      <c r="N476" t="b">
+        <v>0</v>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr"/>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>2026-06-01T14:56:07.658244+00:00</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>305963</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Первенство г. Люберцы "Люберцы ОПЕН"</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>до 19 лет</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>Люберцы</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>IV А</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305963/matches</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305963/dashboard</t>
+        </is>
+      </c>
+      <c r="N477" t="b">
+        <v>0</v>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr"/>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>2026-06-08T06:17:56.629283+00:00</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>305217</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Турнир Кубок "Мостеннис"</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>Воскресенск</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>V А</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305217/matches</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305217/dashboard</t>
+        </is>
+      </c>
+      <c r="N478" t="b">
+        <v>0</v>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>2026-05-11T20:31:12.363735+00:00</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>305505</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Турнир города Москвы А Л Т - ИЮЛЬ (Включен в ЕКП Москомспорта)</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Взрослые</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>V Б</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Олимпийская и ДТ</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305505/matches</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305505/dashboard</t>
+        </is>
+      </c>
+      <c r="N479" t="b">
+        <v>0</v>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>2026-05-11T20:31:44.681774+00:00</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>305652</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Областные Соревнования "Турнир на призы Федерации тенниса Тульской области"</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>Тула</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>III А</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305652/matches</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305652/dashboard</t>
+        </is>
+      </c>
+      <c r="N480" t="b">
+        <v>0</v>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>2026-05-29T06:01:50.436836+00:00</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>305668</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Первенство городского округа Воскресенск на призы TENNIS LIFE</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>Воскресенск</t>
+        </is>
+      </c>
+      <c r="H481" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>IV А</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305668/matches</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305668/dashboard</t>
+        </is>
+      </c>
+      <c r="N481" t="b">
+        <v>0</v>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>2026-05-29T06:01:50.436836+00:00</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>305729</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Турнир, посвященный памяти О. Л. Корнблита</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>Рязань</t>
+        </is>
+      </c>
+      <c r="H482" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>IV Б</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305729/matches</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305729/dashboard</t>
+        </is>
+      </c>
+      <c r="N482" t="b">
+        <v>0</v>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>2026-05-29T06:01:50.436836+00:00</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>305932</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Первенство Центрального Федерального округа</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>Калуга</t>
+        </is>
+      </c>
+      <c r="H483" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>I Б</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305932/matches</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305932/dashboard</t>
+        </is>
+      </c>
+      <c r="N483" t="b">
+        <v>0</v>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr"/>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>2026-06-08T06:17:39.386698+00:00</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>306008</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Чемпионат Одинцовского городского округа Московской области "Гранд Теннис"</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Взрослые</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>Одинцово</t>
+        </is>
+      </c>
+      <c r="H484" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>IV А</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Олимпийская и ДТ</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/306008/matches</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/306008/dashboard</t>
+        </is>
+      </c>
+      <c r="N484" t="b">
+        <v>0</v>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr"/>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>2026-06-08T06:18:13.756561+00:00</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>305578</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Всероссийские соревнования</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Взрослые</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H485" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>I А</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Олимпийская и ДТ</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305578/matches</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305578/dashboard</t>
+        </is>
+      </c>
+      <c r="N485" t="b">
+        <v>0</v>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>2026-05-11T20:31:44.681774+00:00</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>305813</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Кубок Липецкой области Федерации тенниса</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>Липецк</t>
+        </is>
+      </c>
+      <c r="H486" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>III Б</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305813/matches</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305813/dashboard</t>
+        </is>
+      </c>
+      <c r="N486" t="b">
+        <v>0</v>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>2026-05-29T06:01:50.436836+00:00</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>305883</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Первенство Курской области</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>Курск</t>
+        </is>
+      </c>
+      <c r="H487" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>III А</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Олимпийская и ДТ</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305883/matches</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305883/dashboard</t>
+        </is>
+      </c>
+      <c r="N487" t="b">
+        <v>0</v>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr"/>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>2026-05-31T07:08:16.640326+00:00</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>305529</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Первенство Тверской области</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>до 19 лет</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>Вышний Волочек</t>
+        </is>
+      </c>
+      <c r="H488" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>III А</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305529/matches</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305529/dashboard</t>
+        </is>
+      </c>
+      <c r="N488" t="b">
+        <v>0</v>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>2026-05-11T20:31:28.549184+00:00</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>305761</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>"Рязанская ракетка"</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>Рязань</t>
+        </is>
+      </c>
+      <c r="H489" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>IV Б</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305761/matches</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305761/dashboard</t>
+        </is>
+      </c>
+      <c r="N489" t="b">
+        <v>0</v>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>2026-05-29T06:01:50.436836+00:00</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>306021</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Первенство Одинцовского городского округа Московской области "Гранд Теннис"</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>Одинцово</t>
+        </is>
+      </c>
+      <c r="H490" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>IV А</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Олимпийская и ДТ</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/306021/matches</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/306021/dashboard</t>
+        </is>
+      </c>
+      <c r="N490" t="b">
+        <v>0</v>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr"/>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>2026-06-08T06:17:39.386698+00:00</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>306026</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Чемпионат Одинцовского городского округа Московской области "Гранд Теннис"</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Взрослые</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>Одинцово</t>
+        </is>
+      </c>
+      <c r="H491" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>IV А</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Олимпийская и ДТ</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/306026/matches</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/306026/dashboard</t>
+        </is>
+      </c>
+      <c r="N491" t="b">
+        <v>0</v>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr"/>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>2026-06-19T18:20:06.082069+00:00</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>305988</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Кубок Федерации тенниса Рязанской области</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Взрослые</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>Рязань</t>
+        </is>
+      </c>
+      <c r="H492" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>III Б</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305988/matches</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305988/dashboard</t>
+        </is>
+      </c>
+      <c r="N492" t="b">
+        <v>0</v>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr"/>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>2026-06-08T06:18:13.756561+00:00</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>305991</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Кубок Федерации тенниса Рязанской области</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>Рязань</t>
+        </is>
+      </c>
+      <c r="H493" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>III Б</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305991/matches</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305991/dashboard</t>
+        </is>
+      </c>
+      <c r="N493" t="b">
+        <v>0</v>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr"/>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>2026-06-08T06:17:39.386698+00:00</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>306032</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>ЛЕТНИЙ ЧЕМПИОНАТ МОСКВЫ</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Взрослые</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H494" s="2" t="n">
+        <v>46237</v>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>МТ ФТР</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/306032/matches</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/306032/dashboard</t>
+        </is>
+      </c>
+      <c r="N494" t="b">
+        <v>0</v>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr"/>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>2026-06-19T18:20:06.082069+00:00</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>305772</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Турнир Кубок "Мостеннис"</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>Воскресенск</t>
+        </is>
+      </c>
+      <c r="H495" s="2" t="n">
+        <v>46242</v>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>V А</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305772/matches</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305772/dashboard</t>
+        </is>
+      </c>
+      <c r="N495" t="b">
+        <v>0</v>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>2026-05-29T06:01:50.436836+00:00</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>306006</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Турнир выходного дня "Золотые Купола"</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>Сергиев Посад</t>
+        </is>
+      </c>
+      <c r="H496" s="2" t="n">
+        <v>46242</v>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>V А</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/306006/matches</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/306006/dashboard</t>
+        </is>
+      </c>
+      <c r="N496" t="b">
+        <v>0</v>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr"/>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>2026-06-08T06:17:39.386698+00:00</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>305618</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Турнир А Л Т - Август (Включен в ЕКП Москомспорта)</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H497" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>V Б</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Олимпийская и ДТ</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305618/matches</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305618/dashboard</t>
+        </is>
+      </c>
+      <c r="N497" t="b">
+        <v>0</v>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>2026-05-29T06:01:50.436836+00:00</t>
+        </is>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>305784</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Первенство городского округа Воскресенск на призы TENNIS LIFE</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>Воскресенск</t>
+        </is>
+      </c>
+      <c r="H498" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>IV А</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305784/matches</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305784/dashboard</t>
+        </is>
+      </c>
+      <c r="N498" t="b">
+        <v>0</v>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>2026-05-29T06:01:50.436836+00:00</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>305873</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Всероссийские соревнования</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Взрослые</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="H499" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>I А</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Олимпийская и ДТ</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305873/matches</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305873/dashboard</t>
+        </is>
+      </c>
+      <c r="N499" t="b">
+        <v>0</v>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>2026-05-29T06:02:24.670683+00:00</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>305918</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Кубок Федерации тенниса Липецкой области</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>Липецк</t>
+        </is>
+      </c>
+      <c r="H500" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>III Б</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305918/matches</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305918/dashboard</t>
+        </is>
+      </c>
+      <c r="N500" t="b">
+        <v>0</v>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr"/>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>2026-06-08T06:17:39.386698+00:00</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>305978</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Турнир Кубок "Мостеннис"</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>Дмитров</t>
+        </is>
+      </c>
+      <c r="H501" s="2" t="n">
+        <v>46256</v>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>V А</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305978/matches</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305978/dashboard</t>
+        </is>
+      </c>
+      <c r="N501" t="b">
+        <v>0</v>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr"/>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>2026-06-08T06:17:39.386698+00:00</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>305791</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Турнир Кубок "Мостеннис"</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>до 17 лет</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Одиночный</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Центральный ФО</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>Воскресенск</t>
+        </is>
+      </c>
+      <c r="H502" s="2" t="n">
+        <v>46263</v>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Подача заявок</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>V А</t>
+        </is>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Олимпийская</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305791/matches</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>https://rtt.mytennis.online/public/tours/305791/dashboard</t>
+        </is>
+      </c>
+      <c r="N502" t="b">
+        <v>0</v>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>rtt_calendar</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>rtt_failed_links.xlsx</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>2026-05-29T06:01:50.436836+00:00</t>
+        </is>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>2026-06-19T20:45:21.057124+00:00</t>
         </is>
       </c>
     </row>
